--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,27 +585,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>793113815</t>
+          <t>798897163</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8/12/2024</t>
+          <t>10/17/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Correa 1935</t>
+          <t>Juncal 2932</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>793113815</t>
+          <t>798897163</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cambio de poste y retiro de acometidas en desuso. Tarea pasada por T.E</t>
+          <t>Columna Picada y/o Perforada</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -638,46 +638,46 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-58.467635</v>
+        <v>-58.406849</v>
       </c>
       <c r="N3" t="n">
-        <v>-34.541516</v>
+        <v>-34.587756</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>798513070</t>
+          <t>798897384</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10/23/2024</t>
+          <t>10/17/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pedro Ignacio Rivera 4750</t>
+          <t>Peña 3142</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>798513070</t>
+          <t>798897384</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Transferir red y retirar columna.</t>
+          <t>Columna Picada y/o Perforada</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -705,55 +705,51 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-58.483883</v>
+        <v>-58.406396</v>
       </c>
       <c r="N4" t="n">
-        <v>-34.570095</v>
+        <v>-34.585216</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>798897149</t>
+          <t>798897458</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10/16/2024</t>
+          <t>10/15/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>José Andrés Pacheco de Melo 2084</t>
+          <t>Rojas 1091</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>798897149</t>
+          <t>798897458</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso Fuente TECO y retiro de columna</t>
+          <t>Columna fuera de plomo (inclinada)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -776,24 +772,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-58.395656</v>
+        <v>-58.446458</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.590364</v>
+        <v>-34.608741</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -805,27 +801,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>798897163</t>
+          <t>801645051</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10/17/2024</t>
+          <t>12/13/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Juncal 2932</t>
+          <t>Estomba 907</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>798897163</t>
+          <t>801645051</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -840,15 +836,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Columna Picada y/o Perforada</t>
+          <t>Aplomar uno de los postes y desmontar el que esta en desuso</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -856,48 +852,52 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>-58.406849</v>
+        <v>-58.464756</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.587756</v>
+        <v>-34.582693</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>798897384</t>
+          <t>801645141</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10/17/2024</t>
+          <t>12/13/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peña 3142</t>
+          <t>Fraga 1501</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>798897384</t>
+          <t>801645141</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -912,15 +912,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Columna Picada y/o Perforada</t>
+          <t>Aplomar poste de 14 mts</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -928,48 +928,52 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>-58.406396</v>
+        <v>-58.464984</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.585216</v>
+        <v>-34.582783</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>798897458</t>
+          <t>801645368</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10/15/2024</t>
+          <t>12/13/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rojas 1091</t>
+          <t>San Blas 1809</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>798897458</t>
+          <t>801645368</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -984,15 +988,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Columna fuera de plomo (inclinada)</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1000,48 +1004,52 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>-58.446458</v>
+        <v>-58.467767</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.608741</v>
+        <v>-34.604588</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>800367117</t>
+          <t>-51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11/14/2024</t>
+          <t>4/5/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>José Hernández 1610</t>
+          <t>CHARCAS /ALT/ 4176</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>800367117</t>
+          <t>782773317</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1056,68 +1064,68 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t xml:space="preserve">columna de 114mm de nuestra propiedad que esta quebrada y en mal estado, para remplazar ubicada en CHARCAS 4176 </t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>-58.445769</v>
+        <v>-58.421741</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.561327</v>
+        <v>-34.584789</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>800367140</t>
+          <t>-212</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11/14/2024</t>
+          <t>11/7/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Piedras 1374</t>
+          <t>FIGUEROA CNEL APOLINARIO /ALT/ 863</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>800367140</t>
+          <t>799485362</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1132,11 +1140,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir el traspaso</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1145,51 +1153,55 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>-58.376805</v>
+        <v>-58.450579</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.624648</v>
+        <v>-34.607673</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>801645024</t>
+          <t>-254</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>1/7/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fraga 1483</t>
+          <t>BELAUSTEGUI DR LUIS /ALT/ 1185</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>801645024</t>
+          <t>802367713</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1202,13 +1214,9 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1217,23 +1225,23 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-58.464478</v>
+        <v>-58.457158</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.582799</v>
+        <v>-34.605839</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1245,17 +1253,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>801645051</t>
+          <t>-255</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>1/8/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estomba 907</t>
+          <t>Gurruchaga 410</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1265,7 +1273,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>801645051</t>
+          <t>802393948</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1280,11 +1288,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Colocar columna para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1293,23 +1301,23 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-58.464756</v>
+        <v>-58.442601</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.582693</v>
+        <v>-34.597923</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1321,27 +1329,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>801645141</t>
+          <t>803607506</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>2/7/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fraga 1501</t>
+          <t>Paraguay 1312</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>801645141</t>
+          <t>803607506</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1356,11 +1364,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1374,50 +1382,50 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-58.464984</v>
+        <v>-58.385734</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.582783</v>
+        <v>-34.598222</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>801645368</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>2/19/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Blas 1809</t>
+          <t>Arenales 2548</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>801645368</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1436,7 +1444,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1454,46 +1462,46 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-58.467767</v>
+        <v>-58.402534</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.604588</v>
+        <v>-34.593133</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>801645382</t>
+          <t>803608178</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>2/24/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fraga 1788</t>
+          <t>HERNANDEZ JOSE 1451</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>801645382</t>
+          <t>803608178</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1508,7 +1516,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t xml:space="preserve">Cambiar columna 114 y efectuar transferencias base corroida prioridad media </t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1516,7 +1524,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1530,14 +1538,14 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-58.468255</v>
+        <v>-58.443936</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.582762</v>
+        <v>-34.560145</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1549,27 +1557,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-212</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11/7/2024</t>
+          <t>2/24/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FIGUEROA CNEL APOLINARIO /ALT/ 863</t>
+          <t>GUATEMALA /ALT/ 4415</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>799485362</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir el traspaso</t>
+          <t xml:space="preserve">Guatemala 4415 </t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1606,46 +1614,46 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-58.450579</v>
+        <v>-58.421661</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.607673</v>
+        <v>-34.588428</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>803607945</t>
+          <t>-281</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2/19/2025</t>
+          <t>2/26/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jean Jaures 1125</t>
+          <t>SOLER /ALT/ 4517</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>803607945</t>
+          <t>803651203</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1660,20 +1668,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tensor roto</t>
+          <t>columna de 114 con nodo y redes nuestra.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1682,14 +1690,14 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-58.406402</v>
+        <v>-58.423405</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.59669</v>
+        <v>-34.588075</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1701,27 +1709,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>803608208</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>2/28/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LA PAMPA /ALT/ 1001</t>
+          <t>Pichincha 1160</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>803608208</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1736,7 +1744,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna base corroida *prioridad media </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1758,46 +1766,46 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-58.439727</v>
+        <v>-58.397946</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.556261</v>
+        <v>-34.622625</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>803608468</t>
+          <t>803778985</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>3/7/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MOLDES /ALT/ 2143</t>
+          <t>Arenales 3108</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>803608468</t>
+          <t>803778985</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1812,7 +1820,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corroida en base sin riesgo de caída, tienen tendido de fibra, cdo y nap también tienen nodo de telecentro </t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1825,7 +1833,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1834,46 +1842,46 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-58.459804</v>
+        <v>-58.408259</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.563266</v>
+        <v>-34.589265</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>803608178</t>
+          <t>803825124</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>3/7/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HERNANDEZ JOSE /ALT/ 1454</t>
+          <t>José A. Cabrera 3086</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>803608178</t>
+          <t>803825124</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna 114 y efectuar transferencias base corroida prioridad media </t>
+          <t>Desmontar columna y transferir a comunitaria</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1901,7 +1909,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1910,46 +1918,46 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-58.443936</v>
+        <v>-58.41002</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.56026</v>
+        <v>-34.596998</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>-327</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>4/14/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GUATEMALA /ALT/ 4415</t>
+          <t>ROOSEVELT F D ,AV. /ALT/ 5439</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>804634203</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1964,11 +1972,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala 4415 </t>
+          <t>Colocar columna R200 y  dar aviso para el traspaso de nodos. (TECO y TLC)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1977,7 +1985,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1986,46 +1994,46 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-58.421661</v>
+        <v>-58.491074</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.588428</v>
+        <v>-34.575623</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>804787368</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2/28/2025</t>
+          <t>4/17/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pichincha 1160</t>
+          <t>San Blas 2591</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>804787368</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2044,7 +2052,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2062,46 +2070,46 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-58.397946</v>
+        <v>-58.477427</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.622625</v>
+        <v>-34.609261</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>803778985</t>
+          <t>804922147</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3/7/2025</t>
+          <t>4/24/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arenales 3108</t>
+          <t>Av. Álvarez Thomas 1171</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>803778985</t>
+          <t>804922147</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aplomar - Ver previamente con inspector</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2138,46 +2146,46 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-58.408259</v>
+        <v>-58.45793</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.589265</v>
+        <v>-34.578334</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>803825124</t>
+          <t>804922171</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3/7/2025</t>
+          <t>4/24/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>José A. Cabrera 3086</t>
+          <t>Virrey Arredondo 3581</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>803825124</t>
+          <t>804922171</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2192,15 +2200,15 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2210,50 +2218,50 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-58.41002</v>
+        <v>-58.459513</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.596998</v>
+        <v>-34.578019</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>803969308</t>
+          <t>805707165</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3/11/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paraguay 2499</t>
+          <t>Baez 793</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>803969308</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2268,11 +2276,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2290,14 +2298,14 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-58.403255</v>
+        <v>-58.436165</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.597527</v>
+        <v>-34.569081</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2309,27 +2317,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>804018152</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3/14/2025</t>
+          <t>5/6/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carlos Calvo 2765</t>
+          <t>Soldado de la Independencia 1298</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>804018152</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2344,11 +2352,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada - Con fuente teco</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2357,7 +2365,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2366,46 +2374,46 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-58.403882</v>
+        <v>-58.440507</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.621311</v>
+        <v>-34.564016</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>804018226</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3/14/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Humberto 1º 2849</t>
+          <t>Migueletes 1326</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>804018226</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2424,7 +2432,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2442,46 +2450,46 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-58.405077</v>
+        <v>-58.440177</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.622822</v>
+        <v>-34.56291</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>804161204</t>
+          <t>-408</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>5/8/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Av. Hipólito Yrigoyen 3451</t>
+          <t>Larralde 2847</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>804161204</t>
+          <t>805791941</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2496,20 +2504,20 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar columna 114</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2518,46 +2526,46 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-58.415566</v>
+        <v>-58.472267</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.613244</v>
+        <v>-34.551163</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>804161220</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carlos Calvo 4009</t>
+          <t>Paraguay 3765</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>804161220</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2572,11 +2580,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Con prioridad</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2585,7 +2593,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2594,14 +2602,14 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-58.422147</v>
+        <v>-58.416562</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.624736</v>
+        <v>-34.590589</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2613,27 +2621,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Treinta y Tres Orientales 905</t>
+          <t>JUNCAL 4559</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>806926927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2648,11 +2656,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2661,7 +2669,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2670,14 +2678,14 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-58.423229</v>
+        <v>-58.423116</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.625103</v>
+        <v>-34.576984</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2689,27 +2697,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>807044200</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colombres 636</t>
+          <t>11 de Septiembre de 1888 4662</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>807044200</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2724,15 +2732,15 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>CAMBIAR COLUMNA MUY INCLINADA POR POSTE PRFV 400, COLOCAR A 40 CMTS DEL CORDON</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2742,50 +2750,50 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-58.418089</v>
+        <v>-58.467458</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.620313</v>
+        <v>-34.537549</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>807044223</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>5/22/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quito 4292</t>
+          <t>Cucha Cucha 2918</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>807044223</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2800,15 +2808,15 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2822,46 +2830,46 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-58.427201</v>
+        <v>-58.469783</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.617131</v>
+        <v>-34.599214</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>807044233</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maza 836</t>
+          <t>Martin Grandoli 5761</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t xml:space="preserve">ICD30261461 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2876,15 +2884,15 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Desmontar columna de 7 en desuso no colocar nueva queda OT 807044233 solo para el cambio ya realizado el ICD es para el desmonte</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2894,14 +2902,14 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-58.414984</v>
+        <v>-58.487144</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.621386</v>
+        <v>-34.669078</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2917,27 +2925,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>-451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>THAMES 649</t>
+          <t>Uriarte 2426</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>804309655</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2952,7 +2960,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2965,7 +2973,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Nodo/Fuente TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2974,10 +2982,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-58.441405</v>
+        <v>-58.423551</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.594348</v>
+        <v>-34.581258</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2993,27 +3001,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>804427439</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4/1/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Conesa 2195</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>804427439</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3028,11 +3036,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3050,46 +3058,46 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-58.463015</v>
+        <v>-58.420909</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.564505</v>
+        <v>-34.626221</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>804427444</t>
+          <t>-502</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4/1/2025</t>
+          <t>7/7/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cochrane 2864</t>
+          <t>Tagle 2562</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>804427444</t>
+          <t>808036198</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3104,11 +3112,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Colocar columna para pedir traspaso nodo teco</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3117,7 +3125,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3126,46 +3134,46 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-58.507569</v>
+        <v>-58.400188</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.579623</v>
+        <v>-34.583882</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>804468430</t>
+          <t>-506</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4/1/2025</t>
+          <t>7/11/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Honduras 4160</t>
+          <t>Espinosa 591</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>804468430</t>
+          <t>808150511</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3180,11 +3188,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Poste de madera inclinado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3193,23 +3201,23 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-58.422071</v>
+        <v>-58.449</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.594248</v>
+        <v>-34.616077</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3221,27 +3229,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>804568979</t>
+          <t>-508</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Quesada 2710</t>
+          <t>Moldes 2463</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>804568979</t>
+          <t>808194234</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3269,7 +3277,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3278,10 +3286,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-58.466348</v>
+        <v>-58.462281</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.556028</v>
+        <v>-34.560321</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3297,27 +3305,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>804736517</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4/15/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Av. Gral. Mosconi 2490</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>804736517</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3332,7 +3340,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Chocada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3345,7 +3353,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3354,46 +3362,46 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-58.497446</v>
+        <v>-58.402353</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.583455</v>
+        <v>-34.602205</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>804736400</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4/15/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arévalo 2222</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>804736400</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3403,16 +3411,16 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3421,7 +3429,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3430,14 +3438,14 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-58.435751</v>
+        <v>-58.425858</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.5768</v>
+        <v>-34.61629</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3449,27 +3457,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>804787368</t>
+          <t>-556</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4/17/2025</t>
+          <t>8/18/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Blas 2591</t>
+          <t>Bruix 4566</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>804787368</t>
+          <t>809007047</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3506,14 +3514,14 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-58.477427</v>
+        <v>-58.489051</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.609261</v>
+        <v>-34.646531</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3525,17 +3533,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>804838873</t>
+          <t>809156751</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4/21/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Teodoro Vilardebo 2553</t>
+          <t>Av San Martín 5045</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3545,7 +3553,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>804838873</t>
+          <t>809156751</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3560,7 +3568,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Aplomar poste</t>
+          <t>aplomar o cambiar poste de 11 con rienda a pique</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3568,7 +3576,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3582,14 +3590,14 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-58.495251</v>
+        <v>-58.489141</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.606925</v>
+        <v>-34.597221</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3601,27 +3609,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>804922147</t>
+          <t>-565</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Av. Álvarez Thomas 1171</t>
+          <t>Venezuela 3888</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>804922147</t>
+          <t>809168446</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3636,11 +3644,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3658,46 +3666,46 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-58.45793</v>
+        <v>-58.420309</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.578334</v>
+        <v>-34.61767</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>804922171</t>
+          <t>-571</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Virrey Arredondo 3581</t>
+          <t>Alberti 1603</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>804922171</t>
+          <t>809257763</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3712,7 +3720,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3720,7 +3728,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3730,50 +3738,50 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-58.459513</v>
+        <v>-58.39992</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.578019</v>
+        <v>-34.628742</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>804922177</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Moldes 1717</t>
+          <t>JUJUY 1633</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>804922177</t>
+          <t>809257764</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3810,46 +3818,46 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-58.45643</v>
+        <v>-58.401125</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.567121</v>
+        <v>-34.629165</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>804922192</t>
+          <t>-573</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>8/28/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paraguay 4657</t>
+          <t>Juramento 5211</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>804922192</t>
+          <t>809268259</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3886,36 +3894,36 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-58.425642</v>
+        <v>-58.484108</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.583525</v>
+        <v>-34.579014</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>805507192</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4/28/2025</t>
+          <t>9/2/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Virrey Arredondo 2820</t>
+          <t>Pedro Rivera 2546</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3925,7 +3933,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>805507192</t>
+          <t>ICD30612785</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3940,7 +3948,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3953,23 +3961,23 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-58.453939</v>
+        <v>-58.462479</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.571021</v>
+        <v>-34.55765</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3981,27 +3989,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>805655355</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>9/9/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arce 867</t>
+          <t>Uruguay 259</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>805655355</t>
+          <t>809575010</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4029,7 +4037,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4038,14 +4046,14 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-58.436255</v>
+        <v>-58.386393</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.567733</v>
+        <v>-34.605812</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4057,27 +4065,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>805655362</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ortega y Gasset 1781</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>805655362</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4114,14 +4122,14 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-58.432264</v>
+        <v>-58.418823</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.569762</v>
+        <v>-34.602148</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4133,27 +4141,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>-595</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Benjamin Matienzo 1523</t>
+          <t>Montes de oca 1261</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>809800214</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4168,7 +4176,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada evaluar con Pablo el desmonte de la misma ya que por base nos informaron que la zona es subterranea y la columna es vieja</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -4186,18 +4194,18 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-58.432544</v>
+        <v>-58.373931</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.566452</v>
+        <v>-34.642836</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4209,27 +4217,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>805707158</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cañada de Gómez 4433</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>805707158</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4266,14 +4274,14 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-58.479486</v>
+        <v>-58.407029</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.681953</v>
+        <v>-34.62526</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4285,27 +4293,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>-598</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baez 793</t>
+          <t>WASHINGTON 4274</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>809800217</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4338,50 +4346,50 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-58.436165</v>
+        <v>-58.484797</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.569081</v>
+        <v>-34.550364</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5/6/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Soldado de la Independencia 1298</t>
+          <t>FERRARI, ANTONINO M. 1176</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>809837505</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4396,7 +4404,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Picada - Con fuente teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -4409,7 +4417,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4418,46 +4426,46 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-58.440507</v>
+        <v>-58.44406</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.564016</v>
+        <v>-34.626006</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>805707275</t>
+          <t>-601</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cuenca 4262</t>
+          <t>Pedro Goyena 1216</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>805707275</t>
+          <t>809837504</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4494,46 +4502,46 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>-58.503216</v>
+        <v>-58.444685</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.592027</v>
+        <v>-34.62711</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 1336</t>
+          <t>VERA 1021</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>809910087</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4561,7 +4569,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4570,46 +4578,46 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-58.44191</v>
+        <v>-58.442045</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.564245</v>
+        <v>-34.594303</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>806926499</t>
+          <t>-609</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5/15/2025</t>
+          <t>9/24/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 6713</t>
+          <t>Mcal Sucre 1837</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>806926499</t>
+          <t>809972763</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4624,7 +4632,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4632,7 +4640,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4646,46 +4654,46 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-58.460019</v>
+        <v>-58.449934</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.628014</v>
+        <v>-34.560847</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>806981757</t>
+          <t>-610</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>9/24/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rodo 5185</t>
+          <t>Mcal Sucre 1897</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>806981757</t>
+          <t>809972767</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4700,7 +4708,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fuera de plomo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4722,14 +4730,14 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-58.494449</v>
+        <v>-58.450295</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.650431</v>
+        <v>-34.561061</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4741,27 +4749,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>806981754</t>
+          <t>-611</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>9/24/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Corvalan 1195</t>
+          <t>Lafuente 2606</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>806981754</t>
+          <t>809972807</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4776,7 +4784,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Columna fuera de plomo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -4784,7 +4792,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4798,46 +4806,46 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-58.495984</v>
+        <v>-58.444724</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.649551</v>
+        <v>-34.657961</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>807044200</t>
+          <t>-615</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11 de Septiembre de 1888 4662</t>
+          <t>MONTES DE OCA, MANUEL AV. 1079</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>807044200</t>
+          <t>810029907</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4852,7 +4860,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4860,7 +4868,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4870,50 +4878,50 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-58.467458</v>
+        <v>-58.374368</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.537549</v>
+        <v>-34.640512</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>807044207</t>
+          <t>-616</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Moldes 4601</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>807044207</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4928,7 +4936,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -4936,7 +4944,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4950,46 +4958,46 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-58.475622</v>
+        <v>-58.429159</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.542008</v>
+        <v>-34.577821</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>807044212</t>
+          <t>-618</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5/28/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Av. Cabildo 4900</t>
+          <t>Av Cramer 3048</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>807044212</t>
+          <t>810050490</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5004,7 +5012,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5012,7 +5020,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5026,10 +5034,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-58.475021</v>
+        <v>-58.468571</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.54009</v>
+        <v>-34.556427</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5045,27 +5053,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>807044216</t>
+          <t>-620</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Del Barco Centenera 894</t>
+          <t>Luis Viale 3098</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>807044216</t>
+          <t>810056875</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5080,7 +5088,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -5088,7 +5096,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5102,46 +5110,46 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-58.438744</v>
+        <v>-58.477413</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.629929</v>
+        <v>-34.620772</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>807044223</t>
+          <t>-621</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5/22/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cucha Cucha 2918</t>
+          <t>Tres Arroyos 2911</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>807044223</t>
+          <t>810056868</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5156,7 +5164,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5164,7 +5172,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5178,14 +5186,14 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-58.469783</v>
+        <v>-58.476877</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.599214</v>
+        <v>-34.617525</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5197,27 +5205,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>807044233</t>
+          <t>-622</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Martin Grandoli 5761</t>
+          <t>Mariano Acha 2271</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>807044233</t>
+          <t>810056867</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5232,7 +5240,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cambiar o desmontar columna aparentemente en desuso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5254,46 +5262,46 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-58.487144</v>
+        <v>-58.477338</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.669078</v>
+        <v>-34.571921</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>807044260</t>
+          <t>-623</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges 2493</t>
+          <t>Mosconi 3368</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>807044260</t>
+          <t>810061513</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -5316,7 +5324,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5326,50 +5334,50 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-58.421011</v>
+        <v>-58.508377</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.582138</v>
+        <v>-34.590137</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>807044286</t>
+          <t>-624</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Echeandía 5779</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>807044286</t>
+          <t>810093631</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5384,7 +5392,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5406,17 +5414,549 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-58.487136</v>
+        <v>-58.397092</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.667828</v>
+        <v>-34.590173</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>-626</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10/1/2025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Soldado de la Frontera 5371</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Colocar R150 o R200</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>-58.462371</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-34.687152</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
           <t>Boedo</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>-628</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10/1/2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hipolito Yrigoyen 3250</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>810093628</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>-58.412606</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-34.612353</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10/2/2025</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Colocar R150 o R200</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>-58.463851</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-34.606961</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>-629</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10/1/2025</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Colocar R400 para posterior traspaso</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>-58.422406</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-34.577085</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10/6/2025</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TALCAHUANO 990</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>810244456</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>-58.38567</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-34.597173</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>-631</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10/6/2025</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Rincon 789</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>810244458</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>-58.396051</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-34.618206</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>-632</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10/6/2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Gral. Conrado Villegas 5420</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Colocar R150 o R200</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>-58.465521</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-34.681015</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin_Asignar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sin_Asignar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,88 +413,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Proveedor Asignado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Proveedor Asignado</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tipo de tarea</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tipo de Elemento</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de tarea</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Elemento</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Zona</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>N2</t>
         </is>
       </c>
     </row>
@@ -533,38 +531,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>791897762</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>-58.375312</v>
       </c>
@@ -581,6 +579,16 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CON-H</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,38 +613,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>798897163</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Columna Picada y/o Perforada</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>-58.406849</v>
       </c>
@@ -653,6 +661,16 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AGU-J</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,38 +695,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>798897384</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Columna Picada y/o Perforada</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>-58.406396</v>
       </c>
@@ -725,6 +743,16 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>AGU-I</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,38 +777,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>798897458</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Columna fuera de plomo (inclinada)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>-58.446458</v>
       </c>
@@ -797,31 +825,41 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>NRA-B</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>801645051</t>
+          <t>-647</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>10/17/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estomba 907</t>
+          <t>Vicente López 1843</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>801645051</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,53 +869,63 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>01096066</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Aplomar uno de los postes y desmontar el que esta en desuso</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>Colocar R400 para traspasar fuente</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
       <c r="M6" t="n">
-        <v>-58.464756</v>
+        <v>-58.391371</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.582693</v>
+        <v>-34.590472</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RET-A</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>801645141</t>
+          <t>801645051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -887,7 +935,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fraga 1501</t>
+          <t>Estomba 907</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -897,7 +945,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>801645141</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -907,37 +955,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>801645051</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Aplomar poste de 14 mts</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+          <t>Aplomar uno de los postes y desmontar el que esta en desuso</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
       <c r="M7" t="n">
-        <v>-58.464984</v>
+        <v>-58.464756</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.582783</v>
+        <v>-34.582693</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -947,13 +995,23 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ATH-H</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>801645368</t>
+          <t>801645141</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -963,17 +1021,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Blas 1809</t>
+          <t>Fraga 1501</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>801645368</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -983,73 +1041,83 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>801645141</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+          <t>Aplomar poste de 14 mts</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M8" t="n">
-        <v>-58.467767</v>
+        <v>-58.464984</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.604588</v>
+        <v>-34.582783</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>801645368</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4/5/2024</t>
+          <t>12/13/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CHARCAS /ALT/ 4176</t>
+          <t>San Blas 1809</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>782773317</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1059,73 +1127,83 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>801645368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">columna de 114mm de nuestra propiedad que esta quebrada y en mal estado, para remplazar ubicada en CHARCAS 4176 </t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M9" t="n">
-        <v>-58.421741</v>
+        <v>-58.467767</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.584789</v>
+        <v>-34.604588</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>NRA-F</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-212</t>
+          <t>-51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11/7/2024</t>
+          <t>4/5/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIGUEROA CNEL APOLINARIO /ALT/ 863</t>
+          <t>CHARCAS /ALT/ 4176</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>799485362</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1135,73 +1213,83 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>782773317</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir el traspaso</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+          <t xml:space="preserve">columna de 114mm de nuestra propiedad que esta quebrada y en mal estado, para remplazar ubicada en CHARCAS 4176 </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M10" t="n">
-        <v>-58.450579</v>
+        <v>-58.421741</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.607673</v>
+        <v>-34.584789</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>VCR-O</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-254</t>
+          <t>-109</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1/7/2025</t>
+          <t>7/8/2024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BELAUSTEGUI DR LUIS /ALT/ 1185</t>
+          <t>YRIGOYEN HIPOLITO /ALT/ 1938</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>802367713</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1211,69 +1299,83 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>1</v>
+          <t>790175801</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RELEVO INDICA QUE NO HAY COLUMNA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>Pasante</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="n">
-        <v>-58.457158</v>
+        <v>-58.394079</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.605839</v>
+        <v>-34.61051</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CEN-G</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-255</t>
+          <t>-212</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1/8/2025</t>
+          <t>11/7/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gurruchaga 410</t>
+          <t>FIGUEROA CNEL APOLINARIO /ALT/ 863</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>802393948</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1283,37 +1385,37 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>799485362</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de equipos</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
+          <t>Colocar columna para pedir el traspaso</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
           <t>Pasante</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="n">
-        <v>-58.442601</v>
+        <v>-58.450579</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.597923</v>
+        <v>-34.607673</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1323,33 +1425,43 @@
       <c r="P12" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>NRA-H</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>803607506</t>
+          <t>-254</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2/7/2025</t>
+          <t>1/7/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paraguay 1312</t>
+          <t>BELAUSTEGUI DR LUIS /ALT/ 1185</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>803607506</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1359,73 +1471,79 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+          <t>802367713</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M13" t="n">
-        <v>-58.385734</v>
+        <v>-58.457158</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.598222</v>
+        <v>-34.605839</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>NRA-I</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>803607889</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2/19/2025</t>
+          <t>1/8/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arenales 2548</t>
+          <t>Gurruchaga 410</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>803607889</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1435,73 +1553,83 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>802393948</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+          <t>Colocar columna para pedir traspaso de equipos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M14" t="n">
-        <v>-58.402534</v>
+        <v>-58.442601</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.593133</v>
+        <v>-34.597923</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>VCR-J</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>803608178</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>2/19/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HERNANDEZ JOSE 1451</t>
+          <t>Arenales 2548</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>803608178</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1511,53 +1639,63 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna 114 y efectuar transferencias base corroida prioridad media </t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
           <t>Pasante</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
       <c r="M15" t="n">
-        <v>-58.443936</v>
+        <v>-58.402534</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.560145</v>
+        <v>-34.593133</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>AGU-F</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>803608178</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1567,17 +1705,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GUATEMALA /ALT/ 4415</t>
+          <t>HERNANDEZ JOSE 1451</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1587,63 +1725,73 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803608178</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala 4415 </t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+          <t xml:space="preserve">Cambiar columna 114 y efectuar transferencias base corroida prioridad media </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M16" t="n">
-        <v>-58.421661</v>
+        <v>-58.443936</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.588428</v>
+        <v>-34.560145</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>BLO-A</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-281</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2/26/2025</t>
+          <t>2/24/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOLER /ALT/ 4517</t>
+          <t>GUATEMALA /ALT/ 4415</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1653,7 +1801,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>803651203</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1663,37 +1811,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>columna de 114 con nodo y redes nuestra.</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+          <t xml:space="preserve">Guatemala 4415 </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M17" t="n">
-        <v>-58.423405</v>
+        <v>-58.421661</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.588075</v>
+        <v>-34.588428</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1703,33 +1851,43 @@
       <c r="P17" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>VCR-K</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>-281</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2/28/2025</t>
+          <t>2/26/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pichincha 1160</t>
+          <t>SOLER /ALT/ 4517</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1739,73 +1897,83 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803651203</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+          <t>columna de 114 con nodo y redes nuestra.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M18" t="n">
-        <v>-58.397946</v>
+        <v>-58.423405</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.622625</v>
+        <v>-34.588075</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>VCR-K</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>803778985</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3/7/2025</t>
+          <t>2/28/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arenales 3108</t>
+          <t>Pichincha 1160</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>803778985</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1815,46 +1983,56 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M19" t="n">
-        <v>-58.408259</v>
+        <v>-58.397946</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.589265</v>
+        <v>-34.622625</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CEN-N</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -1881,41 +2059,41 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>803825124</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Desmontar columna y transferir a comunitaria</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
       </c>
       <c r="M20" t="n">
         <v>-58.41002</v>
@@ -1933,31 +2111,41 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>VCR-A</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-327</t>
+          <t>-317</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4/14/2025</t>
+          <t>4/9/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROOSEVELT F D ,AV. /ALT/ 5439</t>
+          <t>CIUDAD DE LA PAZ /ALT/ 612</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>804634203</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1967,73 +2155,83 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804569034</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Colocar columna R200 y  dar aviso para el traspaso de nodos. (TECO y TLC)</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+          <t>Terminar traspaso, retirar columna</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M21" t="n">
-        <v>-58.491074</v>
+        <v>-58.445131</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.575623</v>
+        <v>-34.572117</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>COG-C</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>804787368</t>
+          <t>804922171</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4/17/2025</t>
+          <t>4/24/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Blas 2591</t>
+          <t>Virrey Arredondo 3581</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>804787368</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2043,73 +2241,83 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804922171</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+          <t>Aplomar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M22" t="n">
-        <v>-58.477427</v>
+        <v>-58.459513</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.609261</v>
+        <v>-34.578019</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ATH-O</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>804922147</t>
+          <t>805707165</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Av. Álvarez Thomas 1171</t>
+          <t>Baez 793</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>804922147</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2119,73 +2327,83 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
+          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.45793</v>
+        <v>-58.436165</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.578334</v>
+        <v>-34.569081</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>BLO-I</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>804922171</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4/24/2025</t>
+          <t>5/6/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Virrey Arredondo 3581</t>
+          <t>Soldado de la Independencia 1298</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>804922171</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2195,37 +2413,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aplomar</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+          <t>Picada - Con fuente teco</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
       <c r="M24" t="n">
-        <v>-58.459513</v>
+        <v>-58.440507</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.578019</v>
+        <v>-34.564016</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2235,13 +2453,23 @@
       <c r="P24" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>BLO-K</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2251,7 +2479,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baez 793</t>
+          <t>Migueletes 1326</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2261,7 +2489,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ICD30592749</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2271,73 +2499,83 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
       <c r="M25" t="n">
-        <v>-58.436165</v>
+        <v>-58.440177</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.569081</v>
+        <v>-34.56291</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>BLO-K</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>-408</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5/6/2025</t>
+          <t>5/8/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Soldado de la Independencia 1298</t>
+          <t>Larralde 2847</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2347,63 +2585,73 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805791941</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada - Con fuente teco</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+          <t>Aplomar columna 114</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M26" t="n">
-        <v>-58.440507</v>
+        <v>-58.472267</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.564016</v>
+        <v>-34.551163</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>COG-M</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Migueletes 1326</t>
+          <t>Paraguay 3765</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2413,7 +2661,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2423,73 +2671,83 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M27" t="n">
-        <v>-58.440177</v>
+        <v>-58.416562</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.56291</v>
+        <v>-34.590589</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>VCR-K</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-408</t>
+          <t>-428</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5/8/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Larralde 2847</t>
+          <t>Asamblea 301</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>805791941</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2499,53 +2757,63 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926697</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Aplomar columna 114</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+          <t>Chocada en accidente</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M28" t="n">
-        <v>-58.472267</v>
+        <v>-58.429972</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.551163</v>
+        <v>-34.632042</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>PPT-S</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-416</t>
+          <t>-429</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2555,17 +2823,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paraguay 3765</t>
+          <t>Blanco encalada 4362</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>806926557</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2575,46 +2843,56 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926710</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+          <t xml:space="preserve">Cambiar columna 114 base corroida dar prioridad </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M29" t="n">
-        <v>-58.416562</v>
+        <v>-58.47888</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.590589</v>
+        <v>-34.571108</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>ATH-J</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -2641,41 +2919,41 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>806926927</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
       </c>
       <c r="M30" t="n">
         <v>-58.423116</v>
@@ -2693,31 +2971,41 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>VCR-N</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>807044200</t>
+          <t>-440</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11 de Septiembre de 1888 4662</t>
+          <t>LAPRIDA 1374</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>807044200</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2727,73 +3015,83 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807005369</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA MUY INCLINADA POR POSTE PRFV 400, COLOCAR A 40 CMTS DEL CORDON</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
+          <t>Se coloco columna nueva queda pendiente de traspaso</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.467458</v>
+        <v>-58.406585</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.537549</v>
+        <v>-34.592933</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>AGU-B</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>807044223</t>
+          <t>-445</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5/22/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cucha Cucha 2918</t>
+          <t>Joaquin V Gonzalez 4410</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>807044223</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2803,37 +3101,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806945058</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aplomar</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+          <t>Cambiar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M32" t="n">
-        <v>-58.469783</v>
+        <v>-58.51232</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.599214</v>
+        <v>-34.595637</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2843,13 +3141,23 @@
       <c r="P32" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>PUE-O</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>807044233</t>
+          <t>807044200</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2859,17 +3167,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Martin Grandoli 5761</t>
+          <t>11 de Septiembre de 1888 4662</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICD30261461 </t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2879,73 +3187,83 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807044200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Desmontar columna de 7 en desuso no colocar nueva queda OT 807044233 solo para el cambio ya realizado el ICD es para el desmonte</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+          <t>CAMBIAR COLUMNA MUY INCLINADA POR POSTE PRFV 400, COLOCAR A 40 CMTS DEL CORDON</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Desmonte</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
       <c r="M33" t="n">
-        <v>-58.487144</v>
+        <v>-58.467458</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.669078</v>
+        <v>-34.537549</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>BLO-?</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-451</t>
+          <t>807044223</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>5/22/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uriarte 2426</t>
+          <t>Cucha Cucha 2918</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>807044071</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2955,73 +3273,83 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807044223</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+          <t>Aplomar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M34" t="n">
-        <v>-58.423551</v>
+        <v>-58.469783</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.581258</v>
+        <v>-34.599214</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>NRA-F</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>807044233</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Juan 3960</t>
+          <t>Martin Grandoli 5761</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3031,37 +3359,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">ICD30261461 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+          <t>Desmontar columna de 7 en desuso no colocar nueva queda OT 807044233 solo para el cambio ya realizado el ICD es para el desmonte</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M35" t="n">
-        <v>-58.420909</v>
+        <v>-58.487144</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.626221</v>
+        <v>-34.669078</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3071,23 +3399,33 @@
       <c r="P35" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>PAV-L</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-502</t>
+          <t>-451</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7/7/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tagle 2562</t>
+          <t>Uriarte 2426</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3097,7 +3435,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>808036198</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3107,73 +3445,83 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso nodo teco</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M36" t="n">
-        <v>-58.400188</v>
+        <v>-58.423551</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.583882</v>
+        <v>-34.581258</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>VCR-P</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-506</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7/11/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Espinosa 591</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>808150511</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3183,37 +3531,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M37" t="n">
-        <v>-58.449</v>
+        <v>-58.420909</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.616077</v>
+        <v>-34.626221</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3223,33 +3571,43 @@
       <c r="P37" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>PPT-R</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-508</t>
+          <t>-493</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>6/27/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Moldes 2463</t>
+          <t>JUFRE 424</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>808194234</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3259,73 +3617,83 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807817955</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+          <t>Desmontar columna de 168 mm y traspasar redes a columna comunitaria</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M38" t="n">
-        <v>-58.462281</v>
+        <v>-58.432644</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.560321</v>
+        <v>-34.595434</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>VCR-I</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-510</t>
+          <t>-501</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Larrea 590</t>
+          <t>Cabello 3107</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>808194254</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3335,73 +3703,83 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807971967</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
+          <t>Aplomar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.402353</v>
+        <v>-58.405749</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.602205</v>
+        <v>-34.58224</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>AGU-N</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>-502</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>7/7/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>Tagle 2562</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3411,73 +3789,83 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>808036198</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
+          <t>Colocar columna para pedir traspaso nodo teco</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
           <t>Pasante</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
       <c r="M40" t="n">
-        <v>-58.425858</v>
+        <v>-58.400188</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.61629</v>
+        <v>-34.583882</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>AGU-I</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-556</t>
+          <t>-506</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8/18/2025</t>
+          <t>7/11/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bruix 4566</t>
+          <t>Espinosa 591</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>809007047</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3487,7 +3875,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808150511</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3495,65 +3883,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M41" t="n">
-        <v>-58.489051</v>
+        <v>-58.449</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.646531</v>
+        <v>-34.616077</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>NRA-B</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>809156751</t>
+          <t>-508</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Av San Martín 5045</t>
+          <t>Moldes 2463</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>809156751</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3563,73 +3961,83 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808194234</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>aplomar o cambiar poste de 11 con rienda a pique</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
       <c r="M42" t="n">
-        <v>-58.489141</v>
+        <v>-58.462281</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.597221</v>
+        <v>-34.560321</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>COG-J</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-565</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Venezuela 3888</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>809168446</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3639,37 +4047,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PIcada</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M43" t="n">
-        <v>-58.420309</v>
+        <v>-58.402353</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.61767</v>
+        <v>-34.602205</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3679,23 +4087,33 @@
       <c r="P43" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLI-E</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-571</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alberti 1603</t>
+          <t>Carlos Melo 491</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3705,7 +4123,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>809257763</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3715,7 +4133,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808194932</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3723,29 +4141,29 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M44" t="n">
-        <v>-58.39992</v>
+        <v>-58.363292</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.628742</v>
+        <v>-34.642869</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3755,33 +4173,43 @@
       <c r="P44" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CON-E</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-572</t>
+          <t>-517</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>7/16/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JUJUY 1633</t>
+          <t>Av Dorrego 2721</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>809257764</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3791,73 +4219,83 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
+          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>1</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M45" t="n">
-        <v>-58.401125</v>
+        <v>-58.432805</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.629165</v>
+        <v>-34.574345</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>BLO-G</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-573</t>
+          <t>-529</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8/28/2025</t>
+          <t>7/23/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Juramento 5211</t>
+          <t>Libertad 820</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>809268259</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3867,73 +4305,83 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD30189941</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
+          <t>Colocar columna hablar con Pablo si hay dudas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M46" t="n">
-        <v>-58.484108</v>
+        <v>-58.384097</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.579014</v>
+        <v>-34.598913</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>RET-S</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>-556</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>8/18/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>Bruix 4566</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3943,73 +4391,83 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809007047</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M47" t="n">
-        <v>-58.462479</v>
+        <v>-58.489051</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.55765</v>
+        <v>-34.646531</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>PAV-H</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>-571</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9/9/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uruguay 259</t>
+          <t>Alberti 1603</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>809575010</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4019,7 +4477,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809257763</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4027,29 +4485,29 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M48" t="n">
-        <v>-58.386393</v>
+        <v>-58.39992</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.605812</v>
+        <v>-34.628742</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4059,33 +4517,43 @@
       <c r="P48" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>JUJUY 1633</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4095,7 +4563,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809257764</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4103,65 +4571,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M49" t="n">
-        <v>-58.418823</v>
+        <v>-58.401125</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.602148</v>
+        <v>-34.629165</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-595</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/9/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montes de oca 1261</t>
+          <t>Uruguay 259</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>809800214</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4171,37 +4649,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809575010</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Columna picada evaluar con Pablo el desmonte de la misma ya que por base nos informaron que la zona es subterranea y la columna es vieja</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M50" t="n">
-        <v>-58.373931</v>
+        <v>-58.386393</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.642836</v>
+        <v>-34.605812</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4211,33 +4689,43 @@
       <c r="P50" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CEN-Q</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-593</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>Husares 2250</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4247,7 +4735,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809642190</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4255,65 +4743,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
         <v>1</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M51" t="n">
-        <v>-58.407029</v>
+        <v>-58.443269</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.62526</v>
+        <v>-34.552209</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>BLO-B</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-598</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WASHINGTON 4274</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>809800217</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4323,7 +4821,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4331,65 +4829,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
         <v>1</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M52" t="n">
-        <v>-58.484797</v>
+        <v>-58.418823</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.550364</v>
+        <v>-34.602148</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLI-K</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FERRARI, ANTONINO M. 1176</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>809837505</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4399,7 +4907,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4407,38 +4915,48 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
         <v>1</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M53" t="n">
-        <v>-58.44406</v>
+        <v>-58.407029</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.626006</v>
+        <v>-34.62526</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -4465,41 +4983,41 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>809837504</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Picada</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
         <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
       </c>
       <c r="M54" t="n">
         <v>-58.444685</v>
@@ -4517,31 +5035,41 @@
           <t>Capital Sur</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>PCH-D</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>-609</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/24/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VERA 1021</t>
+          <t>Mcal Sucre 1837</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>809910087</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4551,7 +5079,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809972763</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4559,45 +5087,55 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
         <v>1</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M55" t="n">
-        <v>-58.442045</v>
+        <v>-58.449934</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.594303</v>
+        <v>-34.560847</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>BLO-N</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>-609</t>
+          <t>-610</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4607,7 +5145,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mcal Sucre 1837</t>
+          <t>Mcal Sucre 1897</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4617,7 +5155,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>809972763</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4627,7 +5165,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809972767</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4635,29 +5173,29 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>1</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M56" t="n">
-        <v>-58.449934</v>
+        <v>-58.450295</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.560847</v>
+        <v>-34.561061</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4667,13 +5205,23 @@
       <c r="P56" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>BLO-N</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-610</t>
+          <t>-611</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4683,17 +5231,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mcal Sucre 1897</t>
+          <t>Lafuente 2606</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>809972767</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4703,7 +5251,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809972807</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4711,65 +5259,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
         <v>1</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M57" t="n">
-        <v>-58.450295</v>
+        <v>-58.444724</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.561061</v>
+        <v>-34.657961</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>PPT-I</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-611</t>
+          <t>-615</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9/24/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lafuente 2606</t>
+          <t>MONTES DE OCA, MANUEL AV. 1079</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>809972807</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4779,7 +5337,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810029907</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4787,29 +5345,29 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
         <v>1</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M58" t="n">
-        <v>-58.444724</v>
+        <v>-58.374368</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.657961</v>
+        <v>-34.640512</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4819,13 +5377,23 @@
       <c r="P58" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-615</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4835,17 +5403,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1079</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>810029907</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4855,7 +5423,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4863,45 +5431,55 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
         <v>1</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M59" t="n">
-        <v>-58.374368</v>
+        <v>-58.429159</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.640512</v>
+        <v>-34.577821</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>ATH-I</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-616</t>
+          <t>-618</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4911,17 +5489,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Av Cramer 3048</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4931,7 +5509,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810050490</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4939,45 +5517,55 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
         <v>1</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M60" t="n">
-        <v>-58.429159</v>
+        <v>-58.468571</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.577821</v>
+        <v>-34.556427</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>COG-L</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-618</t>
+          <t>-622</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4987,17 +5575,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Av Cramer 3048</t>
+          <t>Mariano Acha 2271</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>810050490</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5007,7 +5595,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810056867</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5015,65 +5603,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
         <v>1</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M61" t="n">
-        <v>-58.468571</v>
+        <v>-58.477338</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.556427</v>
+        <v>-34.571921</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>ATH-J</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-620</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Luis Viale 3098</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>810056875</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5083,73 +5681,83 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>picada</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
+          <t>picada colocar R200 para pedir traspaso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
         <v>1</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
       <c r="M62" t="n">
-        <v>-58.477413</v>
+        <v>-58.397092</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.620772</v>
+        <v>-34.590173</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>RET-D</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-621</t>
+          <t>-626</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tres Arroyos 2911</t>
+          <t>Soldado de la Frontera 5371</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>810056868</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5159,73 +5767,83 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31463420</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
+          <t>Colocar R150 o R200</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
         <v>1</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M63" t="n">
-        <v>-58.476877</v>
+        <v>-58.462371</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.617525</v>
+        <v>-34.687152</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>PAV-T</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-622</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mariano Acha 2271</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>810056867</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5235,7 +5853,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5243,55 +5861,65 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>1</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M64" t="n">
-        <v>-58.477338</v>
+        <v>-58.412606</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.571921</v>
+        <v>-34.612353</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLI-I</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-623</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mosconi 3368</t>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5301,7 +5929,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>810061513</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5311,37 +5939,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31468700</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
+          <t>Colocar R150 o R200</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
         <v>1</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M65" t="n">
-        <v>-58.508377</v>
+        <v>-58.463851</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.590137</v>
+        <v>-34.606961</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5351,33 +5979,43 @@
       <c r="P65" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>NRA-K</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-624</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>810093631</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5387,73 +6025,83 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>picada</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
+          <t>Colocar R400 para posterior traspaso</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
         <v>1</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M66" t="n">
-        <v>-58.397092</v>
+        <v>-58.422406</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.590173</v>
+        <v>-34.577085</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>VCR-M</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-626</t>
+          <t>-630</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Soldado de la Frontera 5371</t>
+          <t>TALCAHUANO 990</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5463,63 +6111,73 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810244456</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
         <v>1</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M67" t="n">
-        <v>-58.462371</v>
+        <v>-58.38567</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.687152</v>
+        <v>-34.597173</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>RET-S</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5529,7 +6187,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5539,37 +6197,37 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Picada</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
+          <t>Colocar R400</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
           <t>Pasante</t>
         </is>
       </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
       <c r="M68" t="n">
-        <v>-58.412606</v>
+        <v>-58.39641</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.612353</v>
+        <v>-34.608561</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5579,33 +6237,43 @@
       <c r="P68" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLI-C</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>-636</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1657</t>
+          <t>GARCIA, JUAN AGUSTIN 1594</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5615,37 +6283,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810307109</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
         <v>1</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M69" t="n">
-        <v>-58.463851</v>
+        <v>-58.465681</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.606961</v>
+        <v>-34.60244</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -5655,33 +6323,43 @@
       <c r="P69" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>NRA-N</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>943</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>BARCA CABO DE HORNOS 6899</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5691,73 +6369,83 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810333113</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
+          <t>Para relevar poste y columna inclinados y cable enroscado en arbol</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
         <v>1</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M70" t="n">
-        <v>-58.422406</v>
+        <v>-58.491592</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.577085</v>
+        <v>-34.679774</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>PAV-M</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-630</t>
+          <t>-643</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TALCAHUANO 990</t>
+          <t>3 de febrero 2699</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>810244456</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5767,7 +6455,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810394753</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5775,65 +6463,75 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
         <v>1</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M71" t="n">
-        <v>-58.38567</v>
+        <v>-58.456816</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.597173</v>
+        <v>-34.553807</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>BLO-D</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-631</t>
+          <t>-646</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rincon 789</t>
+          <t>Andres Lamas 1845</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5843,7 +6541,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810404280</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5851,114 +6549,1154 @@
           <t>Picada</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
         <v>1</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="M72" t="n">
-        <v>-58.396051</v>
+        <v>-58.468222</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.618206</v>
+        <v>-34.608355</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>NRA-K</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-632</t>
+          <t>-651</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gral. Conrado Villegas 5420</t>
+          <t>ALMIRANTE BROWN 1255</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>810421915</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-58.358777</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-34.635704</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CON-G</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>-652</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10/22/2025</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CERRI, DANIEL, GRAL. 1661</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>810421923</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-58.372303</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-34.647218</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>-659</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10/29/2025</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Vera 375</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>810471875</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-58.43668</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-34.600032</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLI-O</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>-662</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ARIAS 2941</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>810490637</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-58.478491</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-34.543969</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>COG-P</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>-663</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2693</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01230744</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Picada con nodo teco</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-58.465679</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-34.63241</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>PCH-H</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-666</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>11/2/2025</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2331</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>810526265</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-58.460681</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-34.63089</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>PCH-J</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>900008676910</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1/23/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ALVEAR, MARCELO T. DE 2101</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-58.39773</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-34.597163</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>RET-H</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LIVERPOOL 2975</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Colocar R150 o R200</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
         <v>1</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="M80" t="n">
+        <v>-58.483044</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-34.583393</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>8453</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="M73" t="n">
-        <v>-58.465521</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-34.681015</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-58.482265</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-34.582718</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BAUNESS 1600</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-58.481148</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-34.583622</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>8455</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LIVERPOOL 2849</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-58.481371</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-34.582578</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LONDRES 4142</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-58.479712</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-34.581443</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GAMARRA y TREVERIS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-58.477099</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-34.582525</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R178"/>
+  <dimension ref="A1:R185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13363,22 +13363,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>900008676910</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ALVEAR, MARCELO T. DE 2101</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13393,10 +13393,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>812440623</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>inclinado base podrida</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -13409,31 +13413,31 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.39773</v>
+        <v>-58.471395</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.597163</v>
+        <v>-34.592451</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>RET-H</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13445,7 +13449,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13455,12 +13459,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13475,12 +13479,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13495,31 +13499,31 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L153" t="n">
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.471395</v>
+        <v>-58.407758</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.592451</v>
+        <v>-34.613793</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13531,7 +13535,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13541,12 +13545,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13561,12 +13565,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13588,24 +13592,24 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.407758</v>
+        <v>-58.481188</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.613793</v>
+        <v>-34.577198</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13617,7 +13621,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-752</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13627,12 +13631,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>RIVADAVIA AV. 5691</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13647,7 +13651,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440563</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13674,24 +13678,24 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.481188</v>
+        <v>-58.445685</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.577198</v>
+        <v>-34.622144</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13703,7 +13707,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-752</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13713,12 +13717,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV. 5691</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13733,7 +13737,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440563</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13760,24 +13764,24 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.445685</v>
+        <v>-58.442723</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.622144</v>
+        <v>-34.56085</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13789,7 +13793,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13799,12 +13803,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13819,12 +13823,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13846,10 +13850,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.442723</v>
+        <v>-58.481187</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.56085</v>
+        <v>-34.548301</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13863,7 +13867,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13875,7 +13879,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13885,12 +13889,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13905,12 +13909,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13932,24 +13936,24 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.481187</v>
+        <v>-58.414586</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.548301</v>
+        <v>-34.630095</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13961,7 +13965,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13971,12 +13975,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13991,12 +13995,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14018,24 +14022,24 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.414586</v>
+        <v>-58.465305</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.630095</v>
+        <v>-34.556794</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14047,22 +14051,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>-765</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>AVALOS 180</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14077,7 +14081,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>812503657</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14104,14 +14108,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.465305</v>
+        <v>-58.465874</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.556794</v>
+        <v>-34.594613</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14121,7 +14125,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14133,7 +14137,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-765</t>
+          <t>-768</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14143,12 +14147,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AVALOS 180</t>
+          <t>CONCORDIA 3581</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14163,12 +14167,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812503657</t>
+          <t>812503649</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14183,17 +14187,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.465874</v>
+        <v>-58.502724</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.594613</v>
+        <v>-34.599311</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -14207,7 +14211,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14219,7 +14223,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-768</t>
+          <t>-767</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14229,7 +14233,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CONCORDIA 3581</t>
+          <t>CONCORDIA 3525</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14249,7 +14253,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812503649</t>
+          <t>812503647</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -14276,10 +14280,10 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.502724</v>
+        <v>-58.502389</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.599311</v>
+        <v>-34.599679</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -14305,7 +14309,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-767</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14315,12 +14319,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CONCORDIA 3525</t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14335,12 +14339,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812503647</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14350,26 +14354,26 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L163" t="n">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.502389</v>
+        <v>-58.464354</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.599679</v>
+        <v>-34.5587</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14379,7 +14383,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14391,22 +14395,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-769</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
+          <t>SAN JUAN AV. 1245</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14426,7 +14430,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14436,7 +14440,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -14448,24 +14452,24 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.464354</v>
+        <v>-58.383649</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.5587</v>
+        <v>-34.622187</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14477,22 +14481,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-771</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 1245</t>
+          <t>SAN BLAS 4112</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14510,11 +14514,7 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -14522,36 +14522,36 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.383649</v>
+        <v>-58.494458</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.622187</v>
+        <v>-34.620078</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>DEV-J</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14563,22 +14563,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-771</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SAN BLAS 4112</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14596,7 +14596,11 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Desplazar Columna</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -14609,31 +14613,31 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.494458</v>
+        <v>-58.423086</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.620078</v>
+        <v>-34.641356</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>DEV-J</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14645,17 +14649,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>-773</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>LA PLATA AV. 2244</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -14680,12 +14684,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -14702,10 +14706,10 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.423086</v>
+        <v>-58.423288</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.641356</v>
+        <v>-34.640581</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14731,7 +14735,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-773</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14741,12 +14745,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2244</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14766,12 +14770,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -14788,10 +14792,10 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.423288</v>
+        <v>-58.422741</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.640581</v>
+        <v>-34.639999</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -14817,22 +14821,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>LIVERPOOL 2975</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14852,7 +14856,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14874,24 +14878,24 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.422741</v>
+        <v>-58.483044</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.639999</v>
+        <v>-34.583393</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14903,7 +14907,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14913,7 +14917,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2975</t>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14960,10 +14964,10 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.483044</v>
+        <v>-58.482265</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.583393</v>
+        <v>-34.582718</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -14989,7 +14993,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14999,7 +15003,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVERPOOL 2903 </t>
+          <t>BAUNESS 1600</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15046,10 +15050,10 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.482265</v>
+        <v>-58.481148</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.582718</v>
+        <v>-34.583622</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -15063,7 +15067,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15075,7 +15079,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15085,7 +15089,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BAUNESS 1600</t>
+          <t>LIVERPOOL 2849</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -15132,10 +15136,10 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.481148</v>
+        <v>-58.481371</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.583622</v>
+        <v>-34.582578</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -15149,7 +15153,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15161,7 +15165,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15171,7 +15175,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2849</t>
+          <t>LONDRES 4142</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15218,10 +15222,10 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.481371</v>
+        <v>-58.479712</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.582578</v>
+        <v>-34.581443</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15235,7 +15239,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15247,7 +15251,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15257,7 +15261,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LONDRES 4142</t>
+          <t>GAMARRA y TREVERIS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -15295,19 +15299,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.479712</v>
+        <v>-58.477099</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.581443</v>
+        <v>-34.582525</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>GAMARRA y TREVERIS</t>
+          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15381,15 +15381,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L175" t="n">
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.477099</v>
+        <v>-58.479692</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.582525</v>
+        <v>-34.586552</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -15403,7 +15407,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15415,7 +15419,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8460 </t>
+          <t>8461</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15425,7 +15429,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
+          <t>BARZANA 1676</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15463,19 +15467,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.479692</v>
+        <v>-58.484405</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.586552</v>
+        <v>-34.583582</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15501,7 +15501,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8461 </t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BARZANA 1676</t>
+          <t>LA PAMPA 5896</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15549,15 +15549,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L177" t="n">
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.484405</v>
+        <v>-58.487925</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.583582</v>
+        <v>-34.584375</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -15571,7 +15575,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-K</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15583,22 +15587,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463 </t>
+          <t xml:space="preserve">8470 </t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LA PAMPA 5896</t>
+          <t>AV. GRAL.BENJAMIN VICTORICA 282</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15611,14 +15615,10 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15639,28 +15639,598 @@
       <c r="L178" t="n">
         <v>1</v>
       </c>
-      <c r="M178" t="n">
-        <v>-58.487925</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-34.584375</v>
-      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>No clasificado, consultar con mantenimiento</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8471 </t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BUCARELLI 1253</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Cambiar columna</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-58.47844</v>
+      </c>
+      <c r="N179" t="n">
+        <v>-34.586982</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
           <t>Paternal</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr">
+      <c r="P179" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>ATH-K</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>ATH-G</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8473 </t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>VIRREY AVILES 3883</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-58.46429</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-34.578287</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>ATH-H</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8474 </t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ESTOMBA 1327</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-58.464844</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-34.578243</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ATH-G</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8475 </t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AV. DE LOS INCAS 3594</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Columna Inclinada </t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-58.463971</v>
+      </c>
+      <c r="N182" t="n">
+        <v>-34.575577</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>ATH-H</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8476 </t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GIRIBONE 2219</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-58.472418</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-34.57958</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>ATH-E</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8568 </t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>HOLMBERG 1053</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Columna Cementar</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-58.468422</v>
+      </c>
+      <c r="N184" t="n">
+        <v>-34.582173</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8569 </t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GARCIA DEL RIO 4577</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-58.489649</v>
+      </c>
+      <c r="N185" t="n">
+        <v>-34.556653</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R185"/>
+  <dimension ref="A1:R205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14481,22 +14481,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-771</t>
+          <t>-773</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SAN BLAS 4112</t>
+          <t>LA PLATA AV. 2244</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14514,10 +14514,14 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>desmonte</t>
+        </is>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -14527,31 +14531,31 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.494458</v>
+        <v>-58.423288</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.620078</v>
+        <v>-34.640581</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>DEV-J</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14563,7 +14567,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14573,12 +14577,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>LIVERPOOL 2975</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14598,7 +14602,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14620,24 +14624,24 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.423086</v>
+        <v>-58.483044</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.641356</v>
+        <v>-34.583393</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14649,22 +14653,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-773</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2244</t>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14684,12 +14688,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -14706,24 +14710,24 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.423288</v>
+        <v>-58.482265</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.640581</v>
+        <v>-34.582718</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14735,22 +14739,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>BAUNESS 1600</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14770,7 +14774,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14792,24 +14796,24 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.422741</v>
+        <v>-58.481148</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.639999</v>
+        <v>-34.583622</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14821,7 +14825,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14831,7 +14835,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2975</t>
+          <t>LIVERPOOL 2849</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -14878,10 +14882,10 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.483044</v>
+        <v>-58.481371</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.583393</v>
+        <v>-34.582578</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -14907,7 +14911,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14917,7 +14921,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVERPOOL 2903 </t>
+          <t>LONDRES 4142</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14964,10 +14968,10 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.482265</v>
+        <v>-58.479712</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.582718</v>
+        <v>-34.581443</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -14981,7 +14985,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -14993,7 +14997,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15003,7 +15007,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BAUNESS 1600</t>
+          <t>GAMARRA y TREVERIS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15041,19 +15045,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.481148</v>
+        <v>-58.477099</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.583622</v>
+        <v>-34.582525</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2849</t>
+          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -15136,10 +15136,10 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.481371</v>
+        <v>-58.479692</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.582578</v>
+        <v>-34.586552</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15165,7 +15165,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LONDRES 4142</t>
+          <t>BARZANA 1676</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15213,19 +15213,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.479712</v>
+        <v>-58.484405</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.581443</v>
+        <v>-34.583582</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15251,7 +15247,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15261,12 +15257,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>GAMARRA y TREVERIS</t>
+          <t>LA PAMPA 5896</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15299,15 +15295,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L174" t="n">
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.477099</v>
+        <v>-58.487925</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.582525</v>
+        <v>-34.584375</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-K</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15333,17 +15333,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t xml:space="preserve">8470 </t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
+          <t>AV. GRAL.BENJAMIN VICTORICA 282</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15361,14 +15361,10 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15389,25 +15385,21 @@
       <c r="L175" t="n">
         <v>1</v>
       </c>
-      <c r="M175" t="n">
-        <v>-58.479692</v>
-      </c>
-      <c r="N175" t="n">
-        <v>-34.586552</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15419,17 +15411,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t xml:space="preserve">8471 </t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BARZANA 1676</t>
+          <t>BUCARELLI 1253</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15447,14 +15439,10 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15467,15 +15455,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.484405</v>
+        <v>-58.47844</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.583582</v>
+        <v>-34.586982</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -15489,7 +15481,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15501,22 +15493,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t xml:space="preserve">8473 </t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LA PAMPA 5896</t>
+          <t>VIRREY AVILES 3883</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15529,19 +15521,15 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -15551,21 +15539,21 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L177" t="n">
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.487925</v>
+        <v>-58.46429</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.584375</v>
+        <v>-34.578287</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15575,7 +15563,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>ATH-K</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15587,7 +15575,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8470 </t>
+          <t xml:space="preserve">8474 </t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15597,7 +15585,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AV. GRAL.BENJAMIN VICTORICA 282</t>
+          <t>ESTOMBA 1327</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -15618,42 +15606,46 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L178" t="n">
         <v>1</v>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>-58.464844</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-34.578243</v>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -15665,7 +15657,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8471 </t>
+          <t xml:space="preserve">8475 </t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15675,7 +15667,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BUCARELLI 1253</t>
+          <t>AV. DE LOS INCAS 3594</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -15696,12 +15688,12 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t xml:space="preserve">Columna Inclinada </t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15718,14 +15710,14 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-58.47844</v>
+        <v>-58.463971</v>
       </c>
       <c r="N179" t="n">
-        <v>-34.586982</v>
+        <v>-34.575577</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -15735,7 +15727,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -15747,7 +15739,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8473 </t>
+          <t xml:space="preserve">8476 </t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15757,7 +15749,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VIRREY AVILES 3883</t>
+          <t>GIRIBONE 2219</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -15793,17 +15785,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L180" t="n">
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-58.46429</v>
+        <v>-58.472418</v>
       </c>
       <c r="N180" t="n">
-        <v>-34.578287</v>
+        <v>-34.57958</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -15817,7 +15809,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -15829,7 +15821,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8474 </t>
+          <t xml:space="preserve">8568 </t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15839,12 +15831,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ESTOMBA 1327</t>
+          <t>HOLMBERG 1053</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15860,7 +15852,7 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Columna Cementar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15870,22 +15862,22 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L181" t="n">
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>-58.464844</v>
+        <v>-58.468422</v>
       </c>
       <c r="N181" t="n">
-        <v>-34.578243</v>
+        <v>-34.582173</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -15899,7 +15891,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -15911,7 +15903,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475 </t>
+          <t xml:space="preserve">8569 </t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15921,12 +15913,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AV. DE LOS INCAS 3594</t>
+          <t>GARCIA DEL RIO 4577</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15942,7 +15934,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna Inclinada </t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15964,14 +15956,14 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-58.463971</v>
+        <v>-58.489649</v>
       </c>
       <c r="N182" t="n">
-        <v>-34.575577</v>
+        <v>-34.556653</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -15981,7 +15973,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -15993,22 +15985,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8476 </t>
+          <t xml:space="preserve">8574 </t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>GIRIBONE 2219</t>
+          <t xml:space="preserve">MANZANARES 4746 </t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16046,14 +16038,14 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-58.472418</v>
+        <v>-58.490797</v>
       </c>
       <c r="N183" t="n">
-        <v>-34.57958</v>
+        <v>-34.558302</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -16063,7 +16055,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16075,17 +16067,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568 </t>
+          <t xml:space="preserve">8575 </t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HOLMBERG 1053</t>
+          <t>LUGONES 3806</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -16106,7 +16098,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Columna Cementar</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -16128,14 +16120,14 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-58.468422</v>
+        <v>-58.490494</v>
       </c>
       <c r="N184" t="n">
-        <v>-34.582173</v>
+        <v>-34.557966</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -16145,7 +16137,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16157,17 +16149,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8569 </t>
+          <t>8576</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4577</t>
+          <t>LUGONES 3866</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -16210,10 +16202,10 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-58.489649</v>
+        <v>-58.490728</v>
       </c>
       <c r="N185" t="n">
-        <v>-34.556653</v>
+        <v>-34.55763</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -16227,10 +16219,1650 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>8577</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUGONES 3992 </t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-58.491397</v>
+      </c>
+      <c r="N186" t="n">
+        <v>-34.556668</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>8578</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUGONES 4030 </t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>-58.491655</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-34.556298</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>8579</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>LUGONES 4090</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>-58.49191</v>
+      </c>
+      <c r="N188" t="n">
+        <v>-34.555928</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>PAROISSIEN 4711</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-58.491698</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-34.556615</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>8581</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MILLER 4016</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-58.492605</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-34.556761</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ACHA MARIANO GRAL 3712</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Sin chequear</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-58.489045</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-34.558226</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
           <t>COG-O</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>8584</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ACHA MARIANO GRAL 3744</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-58.489142</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-34.558086</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>MANZANARES 4512</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-58.488739</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-34.557321</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>8586</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MACHAIN 3709</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-58.488038</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-34.557763</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>8587</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ACHA MARIANO GRAL 3802</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-58.489543</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-34.557511</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>8588</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ACHA MARIANO GRAL 3874</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>-58.489778</v>
+      </c>
+      <c r="N196" t="n">
+        <v>-34.557174</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>8589</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ACHA MARIANO GRAL 3948</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-58.490224</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-34.556533</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>8597</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>JUJUY AV 1717</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-58.400922</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-34.630312</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>8598</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>IGUAZU 590</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-58.405605</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-34.644231</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>PPT-K</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-58.408769</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-34.587342</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>AGU-J</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>8605</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CONDE 3080</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-58.47322</v>
+      </c>
+      <c r="N201" t="n">
+        <v>-34.558645</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>COG-L</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>8606</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>YRIGOYEN HIPOLITO 1934</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-58.394029</v>
+      </c>
+      <c r="N202" t="n">
+        <v>-34.610507</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>CEN-G</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>8609</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>-58.422229</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-34.573148</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>VCR-M</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>8610</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GANDHI MAHATMA 295</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>-58.440568</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-34.6034</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>ALM-N</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AGUIRRE 794</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="n">
+        <v>-58.438085</v>
+      </c>
+      <c r="N205" t="n">
+        <v>-34.595145</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>VCR-H</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R205"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17215,7 +17215,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>IGUAZU 590</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -17268,10 +17268,10 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>-58.400922</v>
+        <v>-58.405605</v>
       </c>
       <c r="N198" t="n">
-        <v>-34.630312</v>
+        <v>-34.644231</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -17297,7 +17297,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17307,12 +17307,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>IGUAZU 590</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -17350,14 +17350,14 @@
         <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>-58.405605</v>
+        <v>-58.408769</v>
       </c>
       <c r="N199" t="n">
-        <v>-34.644231</v>
+        <v>-34.587342</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -17379,7 +17379,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17389,12 +17389,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -17432,24 +17432,24 @@
         <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>-58.408769</v>
+        <v>-58.47322</v>
       </c>
       <c r="N200" t="n">
-        <v>-34.587342</v>
+        <v>-34.558645</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -17461,7 +17461,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>YRIGOYEN HIPOLITO 1934</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -17514,24 +17514,24 @@
         <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>-58.47322</v>
+        <v>-58.394029</v>
       </c>
       <c r="N201" t="n">
-        <v>-34.558645</v>
+        <v>-34.610507</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -17543,7 +17543,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>YRIGOYEN HIPOLITO 1934</t>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -17596,14 +17596,14 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>-58.394029</v>
+        <v>-58.422229</v>
       </c>
       <c r="N202" t="n">
-        <v>-34.610507</v>
+        <v>-34.573148</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -17625,7 +17625,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>GANDHI MAHATMA 295</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -17656,12 +17656,12 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -17678,24 +17678,24 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>-58.422229</v>
+        <v>-58.440568</v>
       </c>
       <c r="N203" t="n">
-        <v>-34.573148</v>
+        <v>-34.6034</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -17707,7 +17707,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>GANDHI MAHATMA 295</t>
+          <t>AGUIRRE 794</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17738,12 +17738,12 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -17760,24 +17760,24 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>-58.440568</v>
+        <v>-58.438085</v>
       </c>
       <c r="N204" t="n">
-        <v>-34.6034</v>
+        <v>-34.595145</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -17789,22 +17789,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t xml:space="preserve">8618 </t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AGUIRRE 794</t>
+          <t>VALLEJOS 4319</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17820,7 +17820,7 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Cambiar Poste de madera a PRFV</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17833,36 +17833,196 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="n">
         <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>-58.438085</v>
+        <v>-58.51875</v>
       </c>
       <c r="N205" t="n">
-        <v>-34.595145</v>
+        <v>-34.598858</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>PUE-P</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8619 </t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>3/17/2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CONCORDIA 3575</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Desmontar Poste y migrar a Columna</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="n">
+        <v>-58.502664</v>
+      </c>
+      <c r="N206" t="n">
+        <v>-34.599377</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8623    </t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>3/17/2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>INCLAN 2402</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-58.398304</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-34.629576</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
           <t>Capital Sur</t>
         </is>
       </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>VCR-H</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R207"/>
+  <dimension ref="A1:R237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9419,7 +9419,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>-618</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9429,12 +9429,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Av Cramer 3048</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>810050490</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9476,24 +9476,24 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.429159</v>
+        <v>-58.468571</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.577821</v>
+        <v>-34.556427</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9505,7 +9505,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-618</t>
+          <t>-622</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Av Cramer 3048</t>
+          <t>Mariano Acha 2271</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>810050490</t>
+          <t>810056867</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9562,14 +9562,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.468571</v>
+        <v>-58.477338</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.556427</v>
+        <v>-34.571921</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9591,22 +9591,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-622</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mariano Acha 2271</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>810056867</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada colocar R200 para pedir traspaso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9648,51 +9648,51 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.477338</v>
+        <v>-58.397092</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.571921</v>
+        <v>-34.590173</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S00936008</t>
+          <t>-626</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>Soldado de la Frontera 5371</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t>ICD31463420</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>picada colocar R200 para pedir traspaso</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9734,14 +9734,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.397092</v>
+        <v>-58.462371</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.590173</v>
+        <v>-34.687152</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9751,19 +9751,19 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>PAV-T</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-626</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Soldado de la Frontera 5371</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ICD31463420</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9820,14 +9820,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.462371</v>
+        <v>-58.412606</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.687152</v>
+        <v>-34.612353</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PAV-T</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9849,7 +9849,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9906,14 +9906,14 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.412606</v>
+        <v>-58.422406</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.612353</v>
+        <v>-34.577085</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>-630</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1657</t>
+          <t>TALCAHUANO 990</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ICD31468700</t>
+          <t>810244456</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9992,24 +9992,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.463851</v>
+        <v>-58.38567</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.606961</v>
+        <v>-34.597173</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>RET-S</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10021,22 +10021,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10075,17 +10075,17 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.422406</v>
+        <v>-58.39641</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.577085</v>
+        <v>-34.608561</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10107,22 +10107,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-630</t>
+          <t>-636</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TALCAHUANO 990</t>
+          <t>GARCIA, JUAN AGUSTIN 1594</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>810244456</t>
+          <t>810307109</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10164,51 +10164,51 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.38567</v>
+        <v>-58.465681</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.597173</v>
+        <v>-34.60244</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>RET-S</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>943</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>BARCA CABO DE HORNOS 6899</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810333113</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Para relevar poste y columna inclinados y cable enroscado en arbol</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10238,26 +10238,26 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.39641</v>
+        <v>-58.491592</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.608561</v>
+        <v>-34.679774</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>PAV-M</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10279,22 +10279,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-636</t>
+          <t>-643</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GARCIA, JUAN AGUSTIN 1594</t>
+          <t>3 de febrero 2699</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>810307109</t>
+          <t>810394753</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10336,14 +10336,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.465681</v>
+        <v>-58.456816</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.60244</v>
+        <v>-34.553807</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10353,34 +10353,34 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>-646</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BARCA CABO DE HORNOS 6899</t>
+          <t>Andres Lamas 1845</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>810333113</t>
+          <t>810404280</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Para relevar poste y columna inclinados y cable enroscado en arbol</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10415,31 +10415,31 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.491592</v>
+        <v>-58.468222</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.679774</v>
+        <v>-34.608355</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>PAV-M</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10451,22 +10451,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-643</t>
+          <t>-651</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3 de febrero 2699</t>
+          <t>ALMIRANTE BROWN 1255</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>810394753</t>
+          <t>810421915</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10508,24 +10508,24 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.456816</v>
+        <v>-58.358777</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.553807</v>
+        <v>-34.635704</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10537,22 +10537,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-646</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Andres Lamas 1845</t>
+          <t>CERRI, DANIEL, GRAL. 1661</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>810404280</t>
+          <t>810421923</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10594,51 +10594,51 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.468222</v>
+        <v>-58.372303</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.608355</v>
+        <v>-34.647218</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-651</t>
+          <t>-659</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ALMIRANTE BROWN 1255</t>
+          <t>Vera 375</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>810421915</t>
+          <t>810471875</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10680,14 +10680,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.358777</v>
+        <v>-58.43668</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.635704</v>
+        <v>-34.600032</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10709,22 +10709,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>-662</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CERRI, DANIEL, GRAL. 1661</t>
+          <t>ARIAS 2941</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>810421923</t>
+          <t>810490637</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10766,51 +10766,51 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.372303</v>
+        <v>-58.478491</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.647218</v>
+        <v>-34.543969</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-659</t>
+          <t>-663</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Vera 375</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2693</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>810471875</t>
+          <t>01230744</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada con nodo teco</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10852,14 +10852,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.43668</v>
+        <v>-58.465679</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.600032</v>
+        <v>-34.63241</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10881,22 +10881,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-662</t>
+          <t>-666</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ARIAS 2941</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2331</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>810490637</t>
+          <t>810526265</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10938,24 +10938,24 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.478491</v>
+        <v>-58.460681</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.543969</v>
+        <v>-34.63089</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10967,22 +10967,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-663</t>
+          <t>-672</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2693</t>
+          <t>Federico Garcia Lorca 255</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>01230744</t>
+          <t>810734112</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Picada con nodo teco</t>
+          <t>Cambiar pasante</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -11024,14 +11024,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.465679</v>
+        <v>-58.445239</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.63241</v>
+        <v>-34.618751</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>NRA-A</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11053,22 +11053,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-666</t>
+          <t>-673</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2331</t>
+          <t>Bauness 2195</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>810526265</t>
+          <t>810787633</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11110,24 +11110,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.460681</v>
+        <v>-58.485702</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.63089</v>
+        <v>-34.576702</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11139,22 +11139,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-672</t>
+          <t>-684</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Federico Garcia Lorca 255</t>
+          <t>LONDRES 4280</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>810734112</t>
+          <t xml:space="preserve">01639693 </t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Cambiar pasante</t>
+          <t>Columna 114 picada en base con receptor óptico propio ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -11196,24 +11196,24 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.445239</v>
+        <v>-58.48081</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.618751</v>
+        <v>-34.582354</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>NRA-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11225,22 +11225,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-673</t>
+          <t>-686</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bauness 2195</t>
+          <t>Pumacahua 292</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>810787633</t>
+          <t>810862736</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11282,24 +11282,24 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.485702</v>
+        <v>-58.453749</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.576702</v>
+        <v>-34.629882</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PCH-A</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11311,22 +11311,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-684</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LONDRES 4280</t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">01639693 </t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Columna 114 picada en base con receptor óptico propio ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11368,51 +11368,51 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.48081</v>
+        <v>-58.397171</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.582354</v>
+        <v>-34.600729</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-686</t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pumacahua 292</t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11427,17 +11427,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>810862736</t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11454,24 +11454,24 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.453749</v>
+        <v>-58.47538</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.629882</v>
+        <v>-34.566015</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PCH-A</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11483,22 +11483,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11533,21 +11533,21 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.397171</v>
+        <v>-58.405835</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.600729</v>
+        <v>-34.583573</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11557,29 +11557,29 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11599,22 +11599,22 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t>corroida colocar columna pedir traspaso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -11626,14 +11626,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.47538</v>
+        <v>-58.491346</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.566015</v>
+        <v>-34.575773</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11655,22 +11655,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>-703</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>Calcena 211</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>811198653</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11705,21 +11705,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.405835</v>
+        <v>-58.456353</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.583573</v>
+        <v>-34.623684</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>NRA-C</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11741,22 +11741,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>corroida colocar columna pedir traspaso</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11786,26 +11786,26 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L133" t="n">
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.491346</v>
+        <v>-58.500094</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.575773</v>
+        <v>-34.626115</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11827,22 +11827,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>-703</t>
+          <t>-707</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Calcena 211</t>
+          <t>Camargo 257</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811198653</t>
+          <t>811238662</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11884,24 +11884,24 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.456353</v>
+        <v>-58.438123</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.623684</v>
+        <v>-34.602541</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>NRA-C</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11913,22 +11913,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11963,31 +11963,31 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.500094</v>
+        <v>-58.412865</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.626115</v>
+        <v>-34.619484</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11999,22 +11999,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>-712</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>Isabel la Católica 963</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t xml:space="preserve">02093829 </t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12056,14 +12056,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.402154</v>
+        <v>-58.372934</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.605295</v>
+        <v>-34.641102</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12073,34 +12073,34 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>-707</t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Camargo 257</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811238662</t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12142,14 +12142,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.438123</v>
+        <v>-58.455182</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.602541</v>
+        <v>-34.559761</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12171,22 +12171,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>-721</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>San Jose 1338</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811454208</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12228,14 +12228,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.412865</v>
+        <v>-58.385762</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.619484</v>
+        <v>-34.623983</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-712</t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Isabel la Católica 963</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12287,14 +12287,10 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">02093829 </t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -12302,58 +12298,58 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.372934</v>
+        <v>-58.484505</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.641102</v>
+        <v>-34.549798</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12373,7 +12369,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12399,25 +12395,21 @@
       <c r="L140" t="n">
         <v>1</v>
       </c>
-      <c r="M140" t="n">
-        <v>-58.455182</v>
-      </c>
-      <c r="N140" t="n">
-        <v>-34.559761</v>
-      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12429,22 +12421,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-721</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Jose 1338</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12459,7 +12451,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811454208</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12486,14 +12478,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.385762</v>
+        <v>-58.432319</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.623983</v>
+        <v>-34.574385</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12503,7 +12495,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12515,22 +12507,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t>Beruti 3012</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12545,10 +12537,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -12556,36 +12552,36 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.484505</v>
+        <v>-58.406584</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.549798</v>
+        <v>-34.589518</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12597,22 +12593,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t>-736</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t>Isabela la Católica 955</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12632,7 +12628,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12642,7 +12638,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12679,22 +12675,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12709,12 +12705,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12729,31 +12725,31 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.432319</v>
+        <v>-58.471803</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.574385</v>
+        <v>-34.592463</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12765,7 +12761,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12775,12 +12771,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12795,12 +12791,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>mal estado</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12810,36 +12806,36 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.406584</v>
+        <v>-58.470581</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.589518</v>
+        <v>-34.592428</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12851,7 +12847,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-736</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12861,12 +12857,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Isabela la Católica 955</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12886,42 +12882,46 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>-58.443393</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-34.549873</v>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>-743</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12983,21 +12983,21 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.471803</v>
+        <v>-58.462095</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.592463</v>
+        <v>-34.579585</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-741</t>
+          <t>-744</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t xml:space="preserve"> Camargo 523</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>811626790</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13069,17 +13069,17 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.470581</v>
+        <v>-58.440392</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.592428</v>
+        <v>-34.60014</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13105,22 +13105,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13135,17 +13135,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -13162,14 +13162,14 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.443393</v>
+        <v>-58.471395</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.549873</v>
+        <v>-34.592451</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13191,22 +13191,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13248,24 +13248,24 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.462095</v>
+        <v>-58.407758</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.579585</v>
+        <v>-34.613793</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13277,22 +13277,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-744</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Camargo 523</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>811626790</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13334,10 +13334,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.440392</v>
+        <v>-58.481188</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.60014</v>
+        <v>-34.577198</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13363,7 +13363,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-752</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>RIVADAVIA AV. 5691</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440563</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13413,31 +13413,31 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.471395</v>
+        <v>-58.445685</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.592451</v>
+        <v>-34.622144</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13449,7 +13449,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13459,12 +13459,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13506,24 +13506,24 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.407758</v>
+        <v>-58.442723</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.613793</v>
+        <v>-34.56085</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13535,7 +13535,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13592,14 +13592,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.481188</v>
+        <v>-58.481187</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.577198</v>
+        <v>-34.548301</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13621,7 +13621,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-752</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV. 5691</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812440563</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13678,10 +13678,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.445685</v>
+        <v>-58.414586</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.622144</v>
+        <v>-34.630095</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13764,10 +13764,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.442723</v>
+        <v>-58.465305</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.56085</v>
+        <v>-34.556794</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13793,22 +13793,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>-765</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>AVALOS 180</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812503657</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13850,14 +13850,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.481187</v>
+        <v>-58.465874</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.548301</v>
+        <v>-34.594613</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13879,22 +13879,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>-768</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>CONCORDIA 3581</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13909,12 +13909,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812503649</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13929,31 +13929,31 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.414586</v>
+        <v>-58.502724</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.630095</v>
+        <v>-34.599311</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13965,22 +13965,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>-767</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>CONCORDIA 3525</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>812503647</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14015,21 +14015,21 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L159" t="n">
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.465305</v>
+        <v>-58.502389</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.556794</v>
+        <v>-34.599679</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14051,7 +14051,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-765</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AVALOS 180</t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812503657</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -14108,14 +14108,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.465874</v>
+        <v>-58.464354</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.594613</v>
+        <v>-34.5587</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14137,22 +14137,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-768</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CONCORDIA 3581</t>
+          <t>SAN JUAN AV. 1245</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812503649</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14182,36 +14182,36 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.502724</v>
+        <v>-58.383649</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.599311</v>
+        <v>-34.622187</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14223,22 +14223,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>-767</t>
+          <t>-773</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CONCORDIA 3525</t>
+          <t>LA PLATA AV. 2244</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14253,17 +14253,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812503647</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -14273,31 +14273,31 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L162" t="n">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.502389</v>
+        <v>-58.423288</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.599679</v>
+        <v>-34.640581</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>-769</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
+          <t>LIVERPOOL 2975</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -14366,14 +14366,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.464354</v>
+        <v>-58.483044</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.5587</v>
+        <v>-34.583393</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14395,22 +14395,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 1245</t>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -14452,24 +14452,24 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.383649</v>
+        <v>-58.482265</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.622187</v>
+        <v>-34.582718</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14481,22 +14481,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-773</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2244</t>
+          <t>BAUNESS 1600</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -14538,24 +14538,24 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.423288</v>
+        <v>-58.481148</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.640581</v>
+        <v>-34.583622</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14567,7 +14567,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2975</t>
+          <t>LIVERPOOL 2849</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -14624,10 +14624,10 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.483044</v>
+        <v>-58.481371</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.583393</v>
+        <v>-34.582578</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVERPOOL 2903 </t>
+          <t>LONDRES 4142</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -14710,10 +14710,10 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.482265</v>
+        <v>-58.479712</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.582718</v>
+        <v>-34.581443</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14739,7 +14739,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BAUNESS 1600</t>
+          <t>GAMARRA y TREVERIS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -14787,19 +14787,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.481148</v>
+        <v>-58.477099</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.583622</v>
+        <v>-34.582525</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -14825,7 +14821,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14835,7 +14831,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LIVERPOOL 2849</t>
+          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -14882,10 +14878,10 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.481371</v>
+        <v>-58.479692</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.582578</v>
+        <v>-34.586552</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -14899,7 +14895,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14911,7 +14907,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14921,7 +14917,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LONDRES 4142</t>
+          <t>BARZANA 1676</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14959,19 +14955,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.479712</v>
+        <v>-58.484405</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.581443</v>
+        <v>-34.583582</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -14997,7 +14989,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15007,12 +14999,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GAMARRA y TREVERIS</t>
+          <t>LA PAMPA 5896</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15045,15 +15037,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L171" t="n">
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.477099</v>
+        <v>-58.487925</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.582525</v>
+        <v>-34.584375</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -15067,7 +15063,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-K</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15079,17 +15075,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t xml:space="preserve">8470 </t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
+          <t>AV. GRAL.BENJAMIN VICTORICA 282</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -15107,14 +15103,10 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15135,25 +15127,21 @@
       <c r="L172" t="n">
         <v>1</v>
       </c>
-      <c r="M172" t="n">
-        <v>-58.479692</v>
-      </c>
-      <c r="N172" t="n">
-        <v>-34.586552</v>
-      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15165,17 +15153,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t xml:space="preserve">8471 </t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BARZANA 1676</t>
+          <t>BUCARELLI 1253</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15193,14 +15181,10 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15213,15 +15197,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.484405</v>
+        <v>-58.47844</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.583582</v>
+        <v>-34.586982</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15235,7 +15223,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15247,22 +15235,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t xml:space="preserve">8473 </t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LA PAMPA 5896</t>
+          <t>VIRREY AVILES 3883</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15275,19 +15263,15 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -15297,21 +15281,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L174" t="n">
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.487925</v>
+        <v>-58.46429</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.584375</v>
+        <v>-34.578287</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15321,7 +15305,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>ATH-K</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15333,7 +15317,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8470 </t>
+          <t xml:space="preserve">8474 </t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15343,7 +15327,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AV. GRAL.BENJAMIN VICTORICA 282</t>
+          <t>ESTOMBA 1327</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15364,42 +15348,46 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L175" t="n">
         <v>1</v>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>-58.464844</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-34.578243</v>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15411,7 +15399,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8471 </t>
+          <t xml:space="preserve">8475 </t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15421,7 +15409,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BUCARELLI 1253</t>
+          <t>AV. DE LOS INCAS 3594</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15442,12 +15430,12 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t xml:space="preserve">Columna Inclinada </t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -15464,14 +15452,14 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.47844</v>
+        <v>-58.463971</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.586982</v>
+        <v>-34.575577</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -15481,7 +15469,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15493,7 +15481,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8473 </t>
+          <t xml:space="preserve">8476 </t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15503,7 +15491,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>VIRREY AVILES 3883</t>
+          <t>GIRIBONE 2219</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -15539,17 +15527,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L177" t="n">
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.46429</v>
+        <v>-58.472418</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.578287</v>
+        <v>-34.57958</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -15563,7 +15551,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15575,7 +15563,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8474 </t>
+          <t xml:space="preserve">8568 </t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15585,12 +15573,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ESTOMBA 1327</t>
+          <t>HOLMBERG 1053</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15606,7 +15594,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Columna Cementar</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15616,22 +15604,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L178" t="n">
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-58.464844</v>
+        <v>-58.468422</v>
       </c>
       <c r="N178" t="n">
-        <v>-34.578243</v>
+        <v>-34.582173</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -15645,7 +15633,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -15657,7 +15645,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475 </t>
+          <t xml:space="preserve">8569 </t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15667,12 +15655,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AV. DE LOS INCAS 3594</t>
+          <t>GARCIA DEL RIO 4577</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15688,7 +15676,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna Inclinada </t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15710,14 +15698,14 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-58.463971</v>
+        <v>-58.489649</v>
       </c>
       <c r="N179" t="n">
-        <v>-34.575577</v>
+        <v>-34.556653</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -15727,7 +15715,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -15739,22 +15727,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8476 </t>
+          <t xml:space="preserve">8574 </t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GIRIBONE 2219</t>
+          <t xml:space="preserve">MANZANARES 4746 </t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15792,14 +15780,14 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-58.472418</v>
+        <v>-58.490797</v>
       </c>
       <c r="N180" t="n">
-        <v>-34.57958</v>
+        <v>-34.558302</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -15809,7 +15797,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -15821,17 +15809,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568 </t>
+          <t xml:space="preserve">8575 </t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HOLMBERG 1053</t>
+          <t>LUGONES 3806</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -15852,7 +15840,7 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Columna Cementar</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15874,14 +15862,14 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>-58.468422</v>
+        <v>-58.490494</v>
       </c>
       <c r="N181" t="n">
-        <v>-34.582173</v>
+        <v>-34.557966</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -15891,7 +15879,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -15903,17 +15891,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8569 </t>
+          <t>8576</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4577</t>
+          <t>LUGONES 3866</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -15956,10 +15944,10 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-58.489649</v>
+        <v>-58.490728</v>
       </c>
       <c r="N182" t="n">
-        <v>-34.556653</v>
+        <v>-34.55763</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -15973,7 +15961,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -15985,7 +15973,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8574 </t>
+          <t>8577</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15995,7 +15983,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANARES 4746 </t>
+          <t xml:space="preserve">LUGONES 3992 </t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -16038,10 +16026,10 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-58.490797</v>
+        <v>-58.491397</v>
       </c>
       <c r="N183" t="n">
-        <v>-34.558302</v>
+        <v>-34.556668</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -16055,7 +16043,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16067,7 +16055,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8575 </t>
+          <t>8578</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16077,7 +16065,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>LUGONES 3806</t>
+          <t xml:space="preserve">LUGONES 4030 </t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -16120,10 +16108,10 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-58.490494</v>
+        <v>-58.491655</v>
       </c>
       <c r="N184" t="n">
-        <v>-34.557966</v>
+        <v>-34.556298</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -16137,7 +16125,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16149,7 +16137,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16159,7 +16147,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LUGONES 3866</t>
+          <t>LUGONES 4090</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -16202,10 +16190,10 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-58.490728</v>
+        <v>-58.49191</v>
       </c>
       <c r="N185" t="n">
-        <v>-34.55763</v>
+        <v>-34.555928</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -16231,7 +16219,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16241,7 +16229,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 3992 </t>
+          <t>PAROISSIEN 4711</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -16262,12 +16250,12 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -16284,10 +16272,10 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>-58.491397</v>
+        <v>-58.491698</v>
       </c>
       <c r="N186" t="n">
-        <v>-34.556668</v>
+        <v>-34.556615</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -16313,7 +16301,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16323,7 +16311,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 4030 </t>
+          <t>MILLER 4016</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -16366,10 +16354,10 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>-58.491655</v>
+        <v>-58.492605</v>
       </c>
       <c r="N187" t="n">
-        <v>-34.556298</v>
+        <v>-34.556761</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -16395,7 +16383,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16405,7 +16393,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LUGONES 4090</t>
+          <t>ACHA MARIANO GRAL 3712</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -16426,17 +16414,17 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Sin chequear</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -16448,10 +16436,10 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-58.49191</v>
+        <v>-58.489045</v>
       </c>
       <c r="N188" t="n">
-        <v>-34.555928</v>
+        <v>-34.558226</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -16465,7 +16453,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -16477,7 +16465,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16487,7 +16475,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PAROISSIEN 4711</t>
+          <t>ACHA MARIANO GRAL 3744</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -16530,10 +16518,10 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-58.491698</v>
+        <v>-58.489142</v>
       </c>
       <c r="N189" t="n">
-        <v>-34.556615</v>
+        <v>-34.558086</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -16547,7 +16535,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -16559,7 +16547,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16569,7 +16557,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MILLER 4016</t>
+          <t>MANZANARES 4512</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -16590,12 +16578,12 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -16612,10 +16600,10 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-58.492605</v>
+        <v>-58.488739</v>
       </c>
       <c r="N190" t="n">
-        <v>-34.556761</v>
+        <v>-34.557321</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -16629,7 +16617,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -16641,7 +16629,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16651,7 +16639,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3712</t>
+          <t>MACHAIN 3709</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -16672,7 +16660,7 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -16682,7 +16670,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Sin chequear</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -16694,10 +16682,10 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>-58.489045</v>
+        <v>-58.488038</v>
       </c>
       <c r="N191" t="n">
-        <v>-34.558226</v>
+        <v>-34.557763</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -16723,7 +16711,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16733,7 +16721,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3744</t>
+          <t>ACHA MARIANO GRAL 3802</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -16776,10 +16764,10 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>-58.489142</v>
+        <v>-58.489543</v>
       </c>
       <c r="N192" t="n">
-        <v>-34.558086</v>
+        <v>-34.557511</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -16805,7 +16793,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16815,7 +16803,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MANZANARES 4512</t>
+          <t>ACHA MARIANO GRAL 3874</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -16836,7 +16824,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -16858,10 +16846,10 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>-58.488739</v>
+        <v>-58.489778</v>
       </c>
       <c r="N193" t="n">
-        <v>-34.557321</v>
+        <v>-34.557174</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -16875,7 +16863,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -16887,7 +16875,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16897,7 +16885,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MACHAIN 3709</t>
+          <t>ACHA MARIANO GRAL 3948</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -16918,7 +16906,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -16940,10 +16928,10 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>-58.488038</v>
+        <v>-58.490224</v>
       </c>
       <c r="N194" t="n">
-        <v>-34.557763</v>
+        <v>-34.556533</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -16957,7 +16945,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -16969,7 +16957,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16979,12 +16967,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3802</t>
+          <t>IGUAZU 590</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -17022,24 +17010,24 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>-58.489543</v>
+        <v>-58.405605</v>
       </c>
       <c r="N195" t="n">
-        <v>-34.557511</v>
+        <v>-34.644231</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -17051,7 +17039,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17061,12 +17049,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3874</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -17082,7 +17070,7 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -17104,24 +17092,24 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>-58.489778</v>
+        <v>-58.408769</v>
       </c>
       <c r="N196" t="n">
-        <v>-34.557174</v>
+        <v>-34.587342</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -17133,7 +17121,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17143,7 +17131,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3948</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -17186,10 +17174,10 @@
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>-58.490224</v>
+        <v>-58.47322</v>
       </c>
       <c r="N197" t="n">
-        <v>-34.556533</v>
+        <v>-34.558645</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -17203,7 +17191,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -17215,7 +17203,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17225,7 +17213,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>IGUAZU 590</t>
+          <t>YRIGOYEN HIPOLITO 1934</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -17268,14 +17256,14 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>-58.405605</v>
+        <v>-58.394029</v>
       </c>
       <c r="N198" t="n">
-        <v>-34.644231</v>
+        <v>-34.610507</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -17285,7 +17273,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -17297,7 +17285,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17307,7 +17295,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17350,14 +17338,14 @@
         <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>-58.408769</v>
+        <v>-58.422229</v>
       </c>
       <c r="N199" t="n">
-        <v>-34.587342</v>
+        <v>-34.573148</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -17367,7 +17355,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -17379,7 +17367,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17389,12 +17377,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>GANDHI MAHATMA 295</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -17410,12 +17398,12 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -17432,14 +17420,14 @@
         <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>-58.47322</v>
+        <v>-58.440568</v>
       </c>
       <c r="N200" t="n">
-        <v>-34.558645</v>
+        <v>-34.6034</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -17449,7 +17437,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -17461,7 +17449,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17471,12 +17459,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>YRIGOYEN HIPOLITO 1934</t>
+          <t>AGUIRRE 794</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -17514,14 +17502,14 @@
         <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>-58.394029</v>
+        <v>-58.438085</v>
       </c>
       <c r="N201" t="n">
-        <v>-34.610507</v>
+        <v>-34.595145</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -17531,7 +17519,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -17543,22 +17531,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t xml:space="preserve">8618 </t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>VALLEJOS 4319</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -17574,7 +17562,7 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Cambiar Poste de madera a PRFV</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17587,33 +17575,29 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="n">
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>-58.422229</v>
+        <v>-58.51875</v>
       </c>
       <c r="N202" t="n">
-        <v>-34.573148</v>
+        <v>-34.598858</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -17625,22 +17609,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t xml:space="preserve">8619 </t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>GANDHI MAHATMA 295</t>
+          <t>CONCORDIA 3575</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -17656,12 +17640,12 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Desmontar Poste y migrar a Columna</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -17678,10 +17662,10 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>-58.440568</v>
+        <v>-58.502664</v>
       </c>
       <c r="N203" t="n">
-        <v>-34.6034</v>
+        <v>-34.599377</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -17695,7 +17679,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -17707,22 +17691,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t xml:space="preserve">8623    </t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AGUIRRE 794</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -17760,14 +17744,14 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>-58.438085</v>
+        <v>-58.398304</v>
       </c>
       <c r="N204" t="n">
-        <v>-34.595145</v>
+        <v>-34.629576</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -17777,7 +17761,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -17789,22 +17773,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8618 </t>
+          <t>R001</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>VALLEJOS 4319</t>
+          <t>EL PROFETA DE LA PAMPA 4523</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17820,7 +17804,7 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Cambiar Poste de madera a PRFV</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17830,22 +17814,26 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L205" t="n">
         <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>-58.51875</v>
+        <v>-58.477211</v>
       </c>
       <c r="N205" t="n">
-        <v>-34.598858</v>
+        <v>-34.652708</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -17855,7 +17843,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PAV-O</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -17867,22 +17855,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8619 </t>
+          <t>00239146</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CONCORDIA 3575</t>
+          <t>POLA 1104</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17898,12 +17886,12 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Desmontar Poste y migrar a Columna</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -17913,21 +17901,21 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>-58.502664</v>
+        <v>-58.50158</v>
       </c>
       <c r="N206" t="n">
-        <v>-34.599377</v>
+        <v>-34.648954</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -17937,7 +17925,7 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -17949,22 +17937,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8623    </t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>BONIFACIO JOSE 2319</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -18002,27 +17990,2491 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>-58.398304</v>
+        <v>-58.459955</v>
       </c>
       <c r="N207" t="n">
-        <v>-34.629576</v>
+        <v>-34.631973</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>PCH-F</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>8422</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>RIVADAVIA AV 5764</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-58.446644</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-34.622863</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>PCH-I</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>00185436</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BESARES 3453</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Cambiar Poste por Columna</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-58.48116</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-34.549119</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>COG-P</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>00191122</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SAN PEDRITO AV 384</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-58.467504</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-34.635231</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>PCH-F</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>01168971</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>NECOCHEA 369</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>-58.364132</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-34.628423</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
           <t>San Telmo</t>
         </is>
       </c>
-      <c r="P207" t="inlineStr">
+      <c r="P211" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>
       </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>PPT-F</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>CON-F</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>00084267</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>MOLDES 920</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-58.44958</v>
+      </c>
+      <c r="N212" t="n">
+        <v>-34.57149</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>COG-?</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>00781500</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>RAVIGNANI EMILIO DR 1498</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>-58.441411</v>
+      </c>
+      <c r="N213" t="n">
+        <v>-34.583443</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>ATH-M</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>00056825</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>LERMA 585</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-58.432774</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-34.593289</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>VCR-I</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>00050599</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-58.418254</v>
+      </c>
+      <c r="N215" t="n">
+        <v>-34.615692</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>ALM-C</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8642   </t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CALCENA 347</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>DESMONTAR COLUMNA Y MIGRAR RED A COLUMNA ALEDAÑA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-58.457348</v>
+      </c>
+      <c r="N216" t="n">
+        <v>-34.622249</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>NRA-C</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>8644</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>GARMENDIA AV. 4945</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-58.465345</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-34.595549</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>ATH-?</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>00223191</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CATAMARCA 254</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-58.406734</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-34.613107</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>CEN-I</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8654 </t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CONCORDIA 3663</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>DESMONTAR POSTE Y MIGRAR RED A COLUMNA EXT.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-58.503291</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-34.598681</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>00201041</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>HABANA 4448</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-58.518808</v>
+      </c>
+      <c r="N220" t="n">
+        <v>-34.601236</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>PUE-P</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>8658</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-58.395567</v>
+      </c>
+      <c r="N221" t="n">
+        <v>-34.615169</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>CEN-C</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>8663</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>MONTENEGRO 1539</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>-58.468478</v>
+      </c>
+      <c r="N222" t="n">
+        <v>-34.587599</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>JEREZ PEDRO DE 430</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-58.467418</v>
+      </c>
+      <c r="N223" t="n">
+        <v>-34.586278</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GARCIA DEL RIO 4457</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-58.488608</v>
+      </c>
+      <c r="N224" t="n">
+        <v>-34.556155</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>8667</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>MACHAIN 3817</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-58.488586</v>
+      </c>
+      <c r="N225" t="n">
+        <v>-34.556965</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>8669</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>MACHAIN 3961</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>-58.489299</v>
+      </c>
+      <c r="N226" t="n">
+        <v>-34.555926</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>8671</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TRONADOR 284</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>-58.470504</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-34.588131</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>8673</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>CADIZ 3715</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>-58.474682</v>
+      </c>
+      <c r="N228" t="n">
+        <v>-34.581396</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>8675</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>LA HAYA 3722</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-58.475097</v>
+      </c>
+      <c r="N229" t="n">
+        <v>-34.581101</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>8676</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>HOLMBERG 979</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>-58.468449</v>
+      </c>
+      <c r="N230" t="n">
+        <v>-34.582898</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>8681</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>GIRARDOT 1384</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-58.466063</v>
+      </c>
+      <c r="N231" t="n">
+        <v>-34.587896</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>CORRIENTES AV 4073</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-58.422076</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-34.60298</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>CLI-K</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>8684</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ESTADO DE PALESTINA 727</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-58.425539</v>
+      </c>
+      <c r="N233" t="n">
+        <v>-34.602286</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>00223023</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SAN JUAN AV. 2201</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-58.396491</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-34.622986</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>CEN-B</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>00275970</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JUJUY AV. 252</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="n">
+        <v>-58.405319</v>
+      </c>
+      <c r="N235" t="n">
+        <v>-34.612931</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>CEN-H</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>00283507</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERRERA 475 </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" t="n">
+        <v>-58.378709</v>
+      </c>
+      <c r="N236" t="n">
+        <v>-34.635064</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>CON-H</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>00289536</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>VALDENEGRO 3554</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>-58.490576</v>
+      </c>
+      <c r="N237" t="n">
+        <v>-34.561508</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>PUE-F</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R237"/>
+  <dimension ref="A1:R243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20069,7 +20069,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20079,12 +20079,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -20097,7 +20097,11 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
       <c r="H233" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -20122,14 +20126,14 @@
         <v>1</v>
       </c>
       <c r="M233" t="n">
-        <v>-58.425539</v>
+        <v>-58.396491</v>
       </c>
       <c r="N233" t="n">
-        <v>-34.602286</v>
+        <v>-34.622986</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -20139,7 +20143,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -20151,7 +20155,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00275970</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20161,7 +20165,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t xml:space="preserve"> JUJUY AV. 252</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -20179,11 +20183,7 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -20208,14 +20208,14 @@
         <v>1</v>
       </c>
       <c r="M234" t="n">
-        <v>-58.396491</v>
+        <v>-58.405319</v>
       </c>
       <c r="N234" t="n">
-        <v>-34.622986</v>
+        <v>-34.612931</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -20237,7 +20237,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>00275970</t>
+          <t>00283507</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20247,12 +20247,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUJUY AV. 252</t>
+          <t xml:space="preserve">HERRERA 475 </t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -20290,14 +20290,14 @@
         <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>-58.405319</v>
+        <v>-58.378709</v>
       </c>
       <c r="N235" t="n">
-        <v>-34.612931</v>
+        <v>-34.635064</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -20319,7 +20319,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>00283507</t>
+          <t>00289536</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA 475 </t>
+          <t>VALDENEGRO 3554</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -20372,24 +20372,24 @@
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>-58.378709</v>
+        <v>-58.490576</v>
       </c>
       <c r="N236" t="n">
-        <v>-34.635064</v>
+        <v>-34.561508</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -20401,22 +20401,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>00289536</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>VALDENEGRO 3554</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -20454,27 +20454,519 @@
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>-58.490576</v>
+        <v>-58.417002</v>
       </c>
       <c r="N237" t="n">
-        <v>-34.561508</v>
+        <v>-34.618613</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>ALM-B</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>00322642</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ESTADO DE PALESTINA 727</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="n">
+        <v>-58.425539</v>
+      </c>
+      <c r="N238" t="n">
+        <v>-34.602286</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>8263</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>MEXICO 3306</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="n">
+        <v>-58.412865</v>
+      </c>
+      <c r="N239" t="n">
+        <v>-34.619484</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>CEN-J</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>8265</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>HUMBERTO 1 1999</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="n">
+        <v>-58.394304</v>
+      </c>
+      <c r="N240" t="n">
+        <v>-34.621645</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>CEN-B</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>08672</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>HERRERA 540</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="n">
+        <v>-58.378264</v>
+      </c>
+      <c r="N241" t="n">
+        <v>-34.636021</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>CON-H</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>8647</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>3/24/2026</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MELIAN AV 4827 </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>-58.487048</v>
+      </c>
+      <c r="N242" t="n">
+        <v>-34.545509</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="P237" t="inlineStr">
+      <c r="P242" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>PUE-F</t>
-        </is>
-      </c>
-      <c r="R237" t="inlineStr">
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>COG-Q</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>8674</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>BRASIL 2509</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>-58.399415</v>
+      </c>
+      <c r="N243" t="n">
+        <v>-34.631112</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R243"/>
+  <dimension ref="A1:R242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19003,7 +19003,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>00201041</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19013,12 +19013,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HABANA 4448</t>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -19034,7 +19034,7 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
-          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -19056,24 +19056,24 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-58.518808</v>
+        <v>-58.395567</v>
       </c>
       <c r="N220" t="n">
-        <v>-34.601236</v>
+        <v>-34.615169</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -19085,7 +19085,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19095,12 +19095,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
+          <t>MONTENEGRO 1539</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -19116,12 +19116,12 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -19138,24 +19138,24 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-58.395567</v>
+        <v>-58.468478</v>
       </c>
       <c r="N221" t="n">
-        <v>-34.615169</v>
+        <v>-34.587599</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -19167,7 +19167,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MONTENEGRO 1539</t>
+          <t>JEREZ PEDRO DE 430</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -19220,10 +19220,10 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-58.468478</v>
+        <v>-58.467418</v>
       </c>
       <c r="N222" t="n">
-        <v>-34.587599</v>
+        <v>-34.586278</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19259,12 +19259,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>JEREZ PEDRO DE 430</t>
+          <t>GARCIA DEL RIO 4457</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -19302,14 +19302,14 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-58.467418</v>
+        <v>-58.488608</v>
       </c>
       <c r="N223" t="n">
-        <v>-34.586278</v>
+        <v>-34.556155</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -19331,7 +19331,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4457</t>
+          <t>MACHAIN 3817</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -19384,10 +19384,10 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-58.488608</v>
+        <v>-58.488586</v>
       </c>
       <c r="N224" t="n">
-        <v>-34.556155</v>
+        <v>-34.556965</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>MACHAIN 3817</t>
+          <t>MACHAIN 3961</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -19466,10 +19466,10 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-58.488586</v>
+        <v>-58.489299</v>
       </c>
       <c r="N225" t="n">
-        <v>-34.556965</v>
+        <v>-34.555926</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -19495,7 +19495,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>MACHAIN 3961</t>
+          <t>TRONADOR 284</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -19548,14 +19548,14 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-58.489299</v>
+        <v>-58.470504</v>
       </c>
       <c r="N226" t="n">
-        <v>-34.555926</v>
+        <v>-34.588131</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -19577,7 +19577,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19587,12 +19587,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>TRONADOR 284</t>
+          <t>CADIZ 3715</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -19630,10 +19630,10 @@
         <v>1</v>
       </c>
       <c r="M227" t="n">
-        <v>-58.470504</v>
+        <v>-58.474682</v>
       </c>
       <c r="N227" t="n">
-        <v>-34.588131</v>
+        <v>-34.581396</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -19659,7 +19659,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CADIZ 3715</t>
+          <t>LA HAYA 3722</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -19712,10 +19712,10 @@
         <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>-58.474682</v>
+        <v>-58.475097</v>
       </c>
       <c r="N228" t="n">
-        <v>-34.581396</v>
+        <v>-34.581101</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LA HAYA 3722</t>
+          <t>HOLMBERG 979</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -19794,14 +19794,14 @@
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>-58.475097</v>
+        <v>-58.468449</v>
       </c>
       <c r="N229" t="n">
-        <v>-34.581101</v>
+        <v>-34.582898</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -19823,7 +19823,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19833,12 +19833,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HOLMBERG 979</t>
+          <t>GIRARDOT 1384</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -19854,12 +19854,12 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -19876,10 +19876,10 @@
         <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>-58.468449</v>
+        <v>-58.466063</v>
       </c>
       <c r="N230" t="n">
-        <v>-34.582898</v>
+        <v>-34.587896</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19915,12 +19915,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>GIRARDOT 1384</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -19958,24 +19958,24 @@
         <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>-58.466063</v>
+        <v>-58.422076</v>
       </c>
       <c r="N231" t="n">
-        <v>-34.587896</v>
+        <v>-34.60298</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -19987,7 +19987,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -20015,7 +20015,11 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
       <c r="H232" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -20040,14 +20044,14 @@
         <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N232" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -20057,7 +20061,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -20069,7 +20073,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00275970</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20079,7 +20083,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t xml:space="preserve"> JUJUY AV. 252</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -20097,11 +20101,7 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -20126,14 +20126,14 @@
         <v>1</v>
       </c>
       <c r="M233" t="n">
-        <v>-58.396491</v>
+        <v>-58.405319</v>
       </c>
       <c r="N233" t="n">
-        <v>-34.622986</v>
+        <v>-34.612931</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -20155,7 +20155,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00275970</t>
+          <t>00283507</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20165,12 +20165,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUJUY AV. 252</t>
+          <t xml:space="preserve">HERRERA 475 </t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -20208,14 +20208,14 @@
         <v>1</v>
       </c>
       <c r="M234" t="n">
-        <v>-58.405319</v>
+        <v>-58.378709</v>
       </c>
       <c r="N234" t="n">
-        <v>-34.612931</v>
+        <v>-34.635064</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -20237,7 +20237,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>00283507</t>
+          <t>00289536</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20247,12 +20247,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA 475 </t>
+          <t>VALDENEGRO 3554</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -20290,24 +20290,24 @@
         <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>-58.378709</v>
+        <v>-58.490576</v>
       </c>
       <c r="N235" t="n">
-        <v>-34.635064</v>
+        <v>-34.561508</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -20319,22 +20319,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>00289536</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>VALDENEGRO 3554</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -20372,24 +20372,24 @@
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>-58.490576</v>
+        <v>-58.417002</v>
       </c>
       <c r="N236" t="n">
-        <v>-34.561508</v>
+        <v>-34.618613</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -20401,7 +20401,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -20454,10 +20454,10 @@
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>-58.417002</v>
+        <v>-58.425539</v>
       </c>
       <c r="N237" t="n">
-        <v>-34.618613</v>
+        <v>-34.602286</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -20483,7 +20483,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -20536,10 +20536,10 @@
         <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>-58.425539</v>
+        <v>-58.412865</v>
       </c>
       <c r="N238" t="n">
-        <v>-34.602286</v>
+        <v>-34.619484</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -20565,7 +20565,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20575,12 +20575,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -20618,14 +20618,14 @@
         <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>-58.412865</v>
+        <v>-58.394304</v>
       </c>
       <c r="N239" t="n">
-        <v>-34.619484</v>
+        <v>-34.621645</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -20647,7 +20647,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>08672</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20657,12 +20657,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>HERRERA 540</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -20688,7 +20688,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -20700,10 +20700,10 @@
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>-58.394304</v>
+        <v>-58.378264</v>
       </c>
       <c r="N240" t="n">
-        <v>-34.621645</v>
+        <v>-34.636021</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -20729,22 +20729,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>08672</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/24/2026</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>HERRERA 540</t>
+          <t xml:space="preserve">MELIAN AV 4827 </t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -20760,7 +20760,7 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -20782,24 +20782,24 @@
         <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>-58.378264</v>
+        <v>-58.487048</v>
       </c>
       <c r="N241" t="n">
-        <v>-34.636021</v>
+        <v>-34.545509</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -20811,22 +20811,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3/24/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELIAN AV 4827 </t>
+          <t>BRASIL 2509</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20842,7 +20842,7 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
-          <t>CAMBIAR POSTE POR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -20864,109 +20864,27 @@
         <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>-58.487048</v>
+        <v>-58.399415</v>
       </c>
       <c r="N242" t="n">
-        <v>-34.545509</v>
+        <v>-34.631112</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>8674</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>3/23/2026</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>BRASIL 2509</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L243" t="n">
-        <v>1</v>
-      </c>
-      <c r="M243" t="n">
-        <v>-58.399415</v>
-      </c>
-      <c r="N243" t="n">
-        <v>-34.631112</v>
-      </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>PPT-F</t>
-        </is>
-      </c>
-      <c r="R243" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R242"/>
+  <dimension ref="A1:R245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20890,6 +20890,252 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11070617 </t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>FONROUGE 1697</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>-58.496881</v>
+      </c>
+      <c r="N243" t="n">
+        <v>-34.653948</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>PAV-H</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>8703</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>RIVADAVIA AV 1985</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" t="n">
+        <v>-58.394609</v>
+      </c>
+      <c r="N244" t="n">
+        <v>-34.609304</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>CLI-B</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>8702</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>JUNCAL 2249</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="n">
+        <v>-58.399319</v>
+      </c>
+      <c r="N245" t="n">
+        <v>-34.592221</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>RET-E</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1RET</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R173"/>
+  <dimension ref="A1:R234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,39 +3231,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>8849</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3/18/2025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Av. Hipólito Yrigoyen 3451</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>804161204</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3/18/2025</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Av. Hipólito Yrigoyen 3451</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Sin Asignar</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>804161204</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Picada</t>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>-58.415566</v>
@@ -10795,7 +10795,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-666</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812971830</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
         <v>-58.516791</v>
@@ -15159,6 +15159,5000 @@
         </is>
       </c>
       <c r="R173" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>8764</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LERMA 299</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-58.430409</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-34.595831</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>CLI-O</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LERMA 311</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-58.430656</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-34.595567</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>CLI-O</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>8766</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ARAOZ 1020</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-58.430374</v>
+      </c>
+      <c r="N176" t="n">
+        <v>-34.595571</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>CLI-O</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>8768</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SALTA 1061</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-58.383028</v>
+      </c>
+      <c r="N177" t="n">
+        <v>-34.620345</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>CEN-A</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>8779</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NAON ROMULO 3405</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-58.480063</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-34.558156</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>COG-N</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>8795</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TERRERO 1390</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-58.463605</v>
+      </c>
+      <c r="N179" t="n">
+        <v>-34.612257</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>NRA-J</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>RINCON 731</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-58.396088</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-34.617527</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>CEN-C</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BARZANA 1685</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-58.484374</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-34.583484</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>8811</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ARGERICH 3685</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-58.496794</v>
+      </c>
+      <c r="N182" t="n">
+        <v>-34.594395</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>PUE-G</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>S00289486</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PARAGUAY 4585</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-58.42498</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-34.584031</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>VCR-P</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>S00325208</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>PARAGUAY 3711</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-58.416117</v>
+      </c>
+      <c r="N184" t="n">
+        <v>-34.590942</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>VCR-C</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>S00337251</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-58.403295</v>
+      </c>
+      <c r="N185" t="n">
+        <v>-34.585041</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>AGU-H</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>S00328975</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EINSTEIN ALBERTO 350</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-58.413179</v>
+      </c>
+      <c r="N186" t="n">
+        <v>-34.649733</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>PPT-H</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>S00334337</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>LUZURIAGA 905</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>-58.388385</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-34.644336</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>CON-K</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>S00337329</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AV SAENZ 1319</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>-58.416649</v>
+      </c>
+      <c r="N188" t="n">
+        <v>-34.656395</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>PPT-H</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>S00355203</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>EREZCANO 2989</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-58.428907</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-34.653746</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>PPT-J</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>S00356525</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>VILLARINO 2225</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-58.376974</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-34.653657</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>CON-I</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>S01150941</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GUALEGUAY 1054</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-58.368312</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-34.632528</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>CON-D</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>S00304430</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BARZANA 1906</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-58.486035</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-34.581541</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>S00363991</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ARCOS 2981</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-58.461029</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-34.552021</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>BLO-Q</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>S00364003</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>OHIGGINS 2715</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-58.45782</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-34.554154</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>BLO-Q</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>S00364886</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-58.434778</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-34.569188</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>BLO-I</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>S00373014</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BYRON 150</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>-58.501659</v>
+      </c>
+      <c r="N196" t="n">
+        <v>-34.63959</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>PAV-F</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>S00374917</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>24 DE NOVIEMBRE 695</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-58.411053</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-34.618979</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>CEN-J</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>S00379764</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>JAURES JEAN 491</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-58.408934</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-34.604273</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>CLI-H</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>S00379996</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SARANDI 1439</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-58.393455</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-34.625779</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>CON-C</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>900009925610</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ASUNCION 3283</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Tensor</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-58.501589</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-34.594928</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>PUE-G</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>8814</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ALCORTA AMANCIO AV 4200</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-58.416172</v>
+      </c>
+      <c r="N201" t="n">
+        <v>-34.657075</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>PPT-H</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>8819</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CUENCA 2082</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Tensor</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-58.487454</v>
+      </c>
+      <c r="N202" t="n">
+        <v>-34.610697</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>NRA-O</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>8823</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SARMIENTO 2108</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>-58.39675</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-34.605996</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>CLI-B</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>8826</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>DONADO 4318</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>-58.490433</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-34.552589</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>8829</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SANCHEZ DE BUSTAMANTE</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>No clasificado, consultar con mantenimiento</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>8831</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>FLORES VENACIO GRAL 4567</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>No clasificado, consultar con mantenimiento</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SANTO TOME 6674</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-58.528021</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-34.627813</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>DEV-O</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GOLETA JULIET 6074</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-58.465488</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-34.689546</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>PAV-T</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SAN MARTIN AV 6117</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-58.501896</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-34.594873</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>PUE-G</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>8845</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>FERNANDEZ DE LA CRUZ 3999</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-58.454481</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-34.668745</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>PAV-?</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>8846</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>RIVADAVIA AV 4245</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>-58.425567</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-34.613382</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>ALM-D</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>8848</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>DIAZ VELEZ AV 4449</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-58.429714</v>
+      </c>
+      <c r="N212" t="n">
+        <v>-34.608645</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>ALM-K</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>LAS CASAS 3989</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>-58.421676</v>
+      </c>
+      <c r="N213" t="n">
+        <v>-34.635878</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>PPT-R</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>8852</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SALCEDO 3541</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-58.415121</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-34.633772</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>PPT-E</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>8853</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>TARIJA 4079</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-58.421804</v>
+      </c>
+      <c r="N215" t="n">
+        <v>-34.629558</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>PPT-R</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>8854</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>TIMBUES 2086</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-58.421835</v>
+      </c>
+      <c r="N216" t="n">
+        <v>-34.63863</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>8855</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>GOMEZ VALENTIN 3684</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-58.416726</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-34.604773</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>CLI-K</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>8858</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PELLEGRINI CARLOS 781</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-58.38119</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-34.599316</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>RTT-?</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>RIVERA FRUCTUOSO GENERAL 3396</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>NORMALIZAR POSTE APARENTEMENTE CAIDO</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-58.444177</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-34.663998</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>PPT-I</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ALVAREZ JULIAN 886</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-58.43109</v>
+      </c>
+      <c r="N220" t="n">
+        <v>-34.597375</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>CLI-O</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>8868</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AV CORRIENTES 5652</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-58.443037</v>
+      </c>
+      <c r="N221" t="n">
+        <v>-34.596062</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>VCR-J</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AV CORRIENTES 5874</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>-58.444912</v>
+      </c>
+      <c r="N222" t="n">
+        <v>-34.594319</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>VCR-?</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>FOURNIER 3090</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-58.417797</v>
+      </c>
+      <c r="N223" t="n">
+        <v>-34.651704</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>PPT-J</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>8686</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CERVANTES 650</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-58.497176</v>
+      </c>
+      <c r="N224" t="n">
+        <v>-34.631131</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>DEV-M</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>S00358190</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>BACACAY 2261</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-58.461722</v>
+      </c>
+      <c r="N225" t="n">
+        <v>-34.625768</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>NRA-E</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>8844</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>MARTINEZ CASTRO 2950</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>DESMONTAR POSTE Y EN LO POSIBLE MIGRAR RED A COLUMNA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>-58.450186</v>
+      </c>
+      <c r="N226" t="n">
+        <v>-34.66107</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>PPT-I</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>S00349916</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>AGUIRRE 790</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>-58.438069</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-34.595162</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>VCR-H</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>S00356245</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GRECIA 4230</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>DESMONTAR POSTE DE MADERA, MIGRAR RED A COLUMNA MAS CERCANA O  COLOCAR NUEVA COLUMNA</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>-58.466813</v>
+      </c>
+      <c r="N228" t="n">
+        <v>-34.541834</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>BLO-S</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>S00356270</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ARCOS 3601</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-58.465195</v>
+      </c>
+      <c r="N229" t="n">
+        <v>-34.54733</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>BLO-R</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>900009955310</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ARISTOBULO DEL VALLE 1111</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>-58.368519</v>
+      </c>
+      <c r="N230" t="n">
+        <v>-34.635343</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>CON-D</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>S00390896</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 2018</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-58.39469</v>
+      </c>
+      <c r="N231" t="n">
+        <v>-34.618394</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>CEN-C</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>S00364996</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>QUINTEROS LIDORO 1316</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-58.450505</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-34.551464</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>BLO-D</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>S00387634</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>AV WARNES 339</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-58.441925</v>
+      </c>
+      <c r="N233" t="n">
+        <v>-34.602367</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>ALM-N</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>S00391032</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>MARISCAL SOLANO LOPEZ 3312</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>DESMONTAR POSTE Y COLOCAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-58.501067</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-34.596916</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R143"/>
+  <dimension ref="A1:R147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12680,6 +12680,334 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>S00356265</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>RIVADAVIA MARTIN, COMODORO 2087</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-58.465653</v>
+      </c>
+      <c r="N144" t="n">
+        <v>-34.546494</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>BLO-R</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>S00387253</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DIAZ, CESAR, GRAL. 4881</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-58.49779</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-34.627626</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>DEV-I</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>S00396906</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MARSELLA 2546</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-58.477848</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-34.582559</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>S00400580</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BORDABEHERE, ENZO 2802</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>CAMBIAR POSTE DE MADERA POR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-58.480405</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-34.600087</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>PUE-A</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R147"/>
+  <dimension ref="A1:R184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13008,6 +13008,2964 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>EXPOSITO</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>JOSE CUBAS 2708</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Corer a línea de medianera por construcción de garage en vecino.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-58.497958</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-34.587254</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>PUE-K</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HALVAREZ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ASUNCION 3719</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Poste quebrado en la base. Sostenido por tendido de red telecom. Con clientes activos</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-58.5078</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-34.598769</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>PUE-P</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MI00001</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LUGONES 2362</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-58.479067</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-34.571679</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>ATH-E</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GG0001</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AV CABILDO 918</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Cambiar columna 114 golpeada provocando dobladora a 1mts del piso.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-58.445962</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-34.569552</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>COG-C</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-58.444908</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-34.607205</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-58.419576</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-34.621289</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-58.430568</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-34.599485</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>-58.437499</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-34.578324</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>-58.435547</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-34.576622</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AREVALO 2006</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-58.373629</v>
+      </c>
+      <c r="N157" t="n">
+        <v>-34.64417</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>-58.444908</v>
+      </c>
+      <c r="N158" t="n">
+        <v>-34.607205</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>-58.419576</v>
+      </c>
+      <c r="N159" t="n">
+        <v>-34.621289</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>-58.430568</v>
+      </c>
+      <c r="N160" t="n">
+        <v>-34.599485</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-58.437499</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-34.578324</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-58.435547</v>
+      </c>
+      <c r="N162" t="n">
+        <v>-34.576622</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AREVALO 2260</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>-58.373629</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-34.64417</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-58.444908</v>
+      </c>
+      <c r="N164" t="n">
+        <v>-34.607205</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>-58.419576</v>
+      </c>
+      <c r="N165" t="n">
+        <v>-34.621289</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-58.430568</v>
+      </c>
+      <c r="N166" t="n">
+        <v>-34.599485</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-58.437499</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-34.578324</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>-58.435547</v>
+      </c>
+      <c r="N168" t="n">
+        <v>-34.576622</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-58.373629</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-34.64417</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AL00001</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ALVAREZ THOMAS AV. 1270</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-58.459453</v>
+      </c>
+      <c r="N170" t="n">
+        <v>-34.57843</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>ATH-O</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>GG00003</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PEDRAZA, MANUELA 2649</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-58.468626</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-34.552938</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>COG-L</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PJ00009</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>THAMES 1516</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-58.431966</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-34.588553</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>HT00001</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CURUPAYTI 2997</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-58.508912</v>
+      </c>
+      <c r="N173" t="n">
+        <v>-34.580858</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>PUE-J</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>LR00001</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BILLINGHURST 1796</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-58.409695</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-34.589662</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>AGU-D</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PJ00040</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>HONDURAS 4822</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-58.428528</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-34.589872</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AF00001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SALGUERO, JERONIMO 1995</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-58.413378</v>
+      </c>
+      <c r="N176" t="n">
+        <v>-34.587254</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>VCR-G</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AL00050</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CULLEN 5771</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-58.49549</v>
+      </c>
+      <c r="N177" t="n">
+        <v>-34.577008</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>PUE-I</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>RB00001</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BELGRANO AV. 3715</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-58.418851</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-34.615716</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>ALM-C</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AM00001</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ARAUJO 2416</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-58.481107</v>
+      </c>
+      <c r="N179" t="n">
+        <v>-34.659759</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>PAV-O</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>GG00035</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FIGUEROA, D. APOLINARIO, CORONEL 1793</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>APLOMAR</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-58.461005</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-34.613152</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>NRA-J</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AM00039</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CASTRO BARROS 852</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-58.419281</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-34.62215</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>LR00044</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CHARCAS 3250</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-58.41175</v>
+      </c>
+      <c r="N182" t="n">
+        <v>-34.592173</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>AGU-C</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>RB12120</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CERRI, DANIEL, GRAL. 1214</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-58.366979</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-34.646341</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>CON-E</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AL25250</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ARENAL, CONCEPCION 3526</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-58.446573</v>
+      </c>
+      <c r="N184" t="n">
+        <v>-34.5842</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>ATH-L</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R184"/>
+  <dimension ref="A1:R210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,7 +3677,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-467</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5999,22 +5999,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-593</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Husares 2250</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>809642190</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6056,24 +6056,24 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.443269</v>
+        <v>-58.418823</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.552209</v>
+        <v>-34.602148</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6085,22 +6085,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6142,14 +6142,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.418823</v>
+        <v>-58.407029</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.602148</v>
+        <v>-34.62526</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6171,22 +6171,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-601</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>Pedro Goyena 1216</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>809837504</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6228,14 +6228,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.407029</v>
+        <v>-58.444685</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.62526</v>
+        <v>-34.62711</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PCH-D</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6257,22 +6257,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-601</t>
+          <t>-603</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pedro Goyena 1216</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>809837504</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna chocada pendiente para instalar un corporativo</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6314,14 +6314,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.444685</v>
+        <v>-58.408551</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.62711</v>
+        <v>-34.599265</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PCH-D</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6343,22 +6343,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-603</t>
+          <t>-609</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/24/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
+          <t>Mcal Sucre 1837</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>809972763</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Columna chocada pendiente para instalar un corporativo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6400,24 +6400,24 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.408551</v>
+        <v>-58.449934</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.599265</v>
+        <v>-34.560847</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>BLO-N</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6429,7 +6429,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-609</t>
+          <t>-610</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mcal Sucre 1837</t>
+          <t>Mcal Sucre 1897</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>809972763</t>
+          <t>809972767</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6486,10 +6486,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.449934</v>
+        <v>-58.450295</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.560847</v>
+        <v>-34.561061</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-610</t>
+          <t>-611</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mcal Sucre 1897</t>
+          <t>Lafuente 2606</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>809972767</t>
+          <t>809972807</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6572,24 +6572,24 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.450295</v>
+        <v>-58.444724</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.561061</v>
+        <v>-34.657961</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>BLO-N</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6601,7 +6601,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-611</t>
+          <t>-612</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lafuente 2606</t>
+          <t>Herrera 588</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6631,14 +6631,10 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>809972807</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Picada</t>
-        </is>
-      </c>
+          <t>809972811</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -6658,10 +6654,10 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.444724</v>
+        <v>-58.378275</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.657961</v>
+        <v>-34.635935</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6675,7 +6671,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6687,17 +6683,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-612</t>
+          <t>-615</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9/24/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Herrera 588</t>
+          <t>MONTES DE OCA, MANUEL AV. 1079</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6717,10 +6713,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>809972811</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>810029907</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -6740,10 +6740,10 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.378275</v>
+        <v>-58.374368</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.635935</v>
+        <v>-34.640512</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-615</t>
+          <t>-618</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1079</t>
+          <t>Av Cramer 3048</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>810029907</t>
+          <t>810050490</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6826,36 +6826,36 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.374368</v>
+        <v>-58.468571</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.640512</v>
+        <v>-34.556427</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-618</t>
+          <t>-622</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Av Cramer 3048</t>
+          <t>Mariano Acha 2271</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>810050490</t>
+          <t>810056867</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6912,14 +6912,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.468571</v>
+        <v>-58.477338</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.556427</v>
+        <v>-34.571921</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6941,22 +6941,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-622</t>
+          <t>-626</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mariano Acha 2271</t>
+          <t>Soldado de la Frontera 5371</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>810056867</t>
+          <t>ICD31463420</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6998,24 +6998,24 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.477338</v>
+        <v>-58.462371</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.571921</v>
+        <v>-34.687152</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>PAV-T</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7027,7 +7027,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-626</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Soldado de la Frontera 5371</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ICD31463420</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7084,14 +7084,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.462371</v>
+        <v>-58.412606</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.687152</v>
+        <v>-34.612353</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PAV-T</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7170,14 +7170,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.412606</v>
+        <v>-58.422406</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.612353</v>
+        <v>-34.577085</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7199,22 +7199,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>-630</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>TALCAHUANO 990</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>810244456</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7256,14 +7256,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.422406</v>
+        <v>-58.38567</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.577085</v>
+        <v>-34.597173</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>RET-S</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7285,22 +7285,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-630</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TALCAHUANO 990</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>810244456</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7339,17 +7339,17 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.38567</v>
+        <v>-58.39641</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.597173</v>
+        <v>-34.608561</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>RET-S</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7371,22 +7371,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>-636</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>GARCIA, JUAN AGUSTIN 1594</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810307109</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7425,39 +7425,39 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.39641</v>
+        <v>-58.465681</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.608561</v>
+        <v>-34.60244</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>-636</t>
+          <t>943</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GARCIA, JUAN AGUSTIN 1594</t>
+          <t>BARCA CABO DE HORNOS 6899</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>810307109</t>
+          <t>810333113</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Para relevar poste y columna inclinados y cable enroscado en arbol</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7507,58 +7507,58 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.465681</v>
+        <v>-58.491592</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.60244</v>
+        <v>-34.679774</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>PAV-M</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>-643</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BARCA CABO DE HORNOS 6899</t>
+          <t>3 de febrero 2699</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>810333113</t>
+          <t>810394753</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Para relevar poste y columna inclinados y cable enroscado en arbol</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7593,31 +7593,31 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.491592</v>
+        <v>-58.456816</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.679774</v>
+        <v>-34.553807</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PAV-M</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-643</t>
+          <t>-646</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3 de febrero 2699</t>
+          <t>Andres Lamas 1845</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>810394753</t>
+          <t>810404280</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7686,14 +7686,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.456816</v>
+        <v>-58.468222</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.553807</v>
+        <v>-34.608355</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-646</t>
+          <t>-651</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Andres Lamas 1845</t>
+          <t>ALMIRANTE BROWN 1255</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>810404280</t>
+          <t>810421915</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7772,24 +7772,24 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.468222</v>
+        <v>-58.358777</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.608355</v>
+        <v>-34.635704</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7801,7 +7801,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-651</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ALMIRANTE BROWN 1255</t>
+          <t>CERRI, DANIEL, GRAL. 1661</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>810421915</t>
+          <t>810421923</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7858,10 +7858,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.358777</v>
+        <v>-58.372303</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.635704</v>
+        <v>-34.647218</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7875,34 +7875,34 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>-659</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CERRI, DANIEL, GRAL. 1661</t>
+          <t>Vera 375</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>810421923</t>
+          <t>810471875</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7944,14 +7944,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.372303</v>
+        <v>-58.43668</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.647218</v>
+        <v>-34.600032</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7961,34 +7961,34 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-659</t>
+          <t>-662</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vera 375</t>
+          <t>ARIAS 2941</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>810471875</t>
+          <t>810490637</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8030,24 +8030,24 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.43668</v>
+        <v>-58.478491</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.600032</v>
+        <v>-34.543969</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,7 +8059,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-662</t>
+          <t>-663</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ARIAS 2941</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2693</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>810490637</t>
+          <t>01230744</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada con nodo teco</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8116,24 +8116,24 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.478491</v>
+        <v>-58.465679</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.543969</v>
+        <v>-34.63241</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8145,17 +8145,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-663</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2693</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2331</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01230744</t>
+          <t>810526265</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Picada con nodo teco</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8202,10 +8202,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.465679</v>
+        <v>-58.460681</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.63241</v>
+        <v>-34.63089</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8231,22 +8231,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>-672</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2331</t>
+          <t>Federico Garcia Lorca 255</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>810526265</t>
+          <t>810734112</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>Cambiar pasante</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8288,14 +8288,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.460681</v>
+        <v>-58.445239</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.63089</v>
+        <v>-34.618751</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>NRA-A</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,22 +8317,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-672</t>
+          <t>-673</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Federico Garcia Lorca 255</t>
+          <t>Bauness 2195</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>810734112</t>
+          <t>810787633</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Cambiar pasante</t>
+          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8374,24 +8374,24 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.445239</v>
+        <v>-58.485702</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.618751</v>
+        <v>-34.576702</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>NRA-A</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,22 +8403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>-673</t>
+          <t>-684</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bauness 2195</t>
+          <t>LONDRES 4280</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>810787633</t>
+          <t xml:space="preserve">01639693 </t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
+          <t>Columna 114 picada en base con receptor óptico propio ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8460,10 +8460,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.485702</v>
+        <v>-58.48081</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.576702</v>
+        <v>-34.582354</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-684</t>
+          <t>-686</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LONDRES 4280</t>
+          <t>Pumacahua 292</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">01639693 </t>
+          <t>810862736</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Columna 114 picada en base con receptor óptico propio ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8546,24 +8546,24 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.48081</v>
+        <v>-58.453749</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.582354</v>
+        <v>-34.629882</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PCH-A</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-686</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pumacahua 292</t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>810862736</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8632,14 +8632,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.453749</v>
+        <v>-58.397171</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.629882</v>
+        <v>-34.600729</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8649,34 +8649,34 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>PCH-A</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8691,17 +8691,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8718,51 +8718,51 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.397171</v>
+        <v>-58.47538</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.600729</v>
+        <v>-34.566015</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8777,17 +8777,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8797,31 +8797,31 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.47538</v>
+        <v>-58.405835</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.566015</v>
+        <v>-34.583573</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,22 +8833,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida colocar columna pedir traspaso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8878,36 +8878,36 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.405835</v>
+        <v>-58.491346</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.583573</v>
+        <v>-34.575773</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,22 +8919,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>-703</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>Calcena 211</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>811198653</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>corroida colocar columna pedir traspaso</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8976,24 +8976,24 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.491346</v>
+        <v>-58.456353</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.575773</v>
+        <v>-34.623684</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>NRA-C</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,22 +9005,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>-703</t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Calcena 211</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811198653</t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9055,31 +9055,31 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.456353</v>
+        <v>-58.500094</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.623684</v>
+        <v>-34.626115</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>NRA-C</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>-707</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t>Camargo 257</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811238662</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9141,21 +9141,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.500094</v>
+        <v>-58.438123</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.626115</v>
+        <v>-34.602541</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,22 +9177,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-707</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Camargo 257</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811238662</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9234,24 +9234,24 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.438123</v>
+        <v>-58.412865</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.602541</v>
+        <v>-34.619484</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>-712</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>Isabel la Católica 963</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t xml:space="preserve">02093829 </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9320,14 +9320,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.412865</v>
+        <v>-58.372934</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.619484</v>
+        <v>-34.641102</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9337,34 +9337,34 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-712</t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Isabel la Católica 963</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02093829 </t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9406,51 +9406,51 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.372934</v>
+        <v>-58.455182</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.641102</v>
+        <v>-34.559761</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>-721</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t>San Jose 1338</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>811454208</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9492,24 +9492,24 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.455182</v>
+        <v>-58.385762</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.559761</v>
+        <v>-34.623983</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,22 +9521,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-721</t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose 1338</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9551,14 +9551,10 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811454208</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -9571,31 +9567,31 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.385762</v>
+        <v>-58.484505</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.623983</v>
+        <v>-34.549798</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9617,12 +9613,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9637,10 +9633,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -9653,31 +9653,27 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>1</v>
       </c>
-      <c r="M108" t="n">
-        <v>-58.484505</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-34.549798</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9685,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,12 +9695,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9719,12 +9715,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9745,21 +9741,25 @@
       <c r="L109" t="n">
         <v>1</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>-58.432319</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-34.574385</v>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9771,22 +9771,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>Beruti 3012</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9825,17 +9825,17 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.432319</v>
+        <v>-58.406584</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.574385</v>
+        <v>-34.589518</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9857,7 +9857,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>-736</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>Isabela la Católica 955</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812971830</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9911,27 +9911,23 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>-58.406584</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-34.589518</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9943,7 +9939,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>-736</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9953,12 +9949,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Isabela la Católica 955</t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9973,12 +9969,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>812971830</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9988,32 +9984,36 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>-58.471803</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-34.592463</v>
+      </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>mal estado</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10082,10 +10082,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.471803</v>
+        <v>-58.470581</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.592463</v>
+        <v>-34.592428</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-741</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10141,17 +10141,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -10168,14 +10168,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.470581</v>
+        <v>-58.443393</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.592428</v>
+        <v>-34.549873</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10197,7 +10197,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>S00417323</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10227,17 +10227,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -10247,21 +10247,21 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.443393</v>
+        <v>-58.462095</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.549873</v>
+        <v>-34.579585</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10283,7 +10283,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>-744</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t xml:space="preserve"> Camargo 523</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>811626790</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10340,14 +10340,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.462095</v>
+        <v>-58.440392</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.579585</v>
+        <v>-34.60014</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10369,22 +10369,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-744</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Camargo 523</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811626790</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10426,24 +10426,24 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.440392</v>
+        <v>-58.407758</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.60014</v>
+        <v>-34.613793</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10455,7 +10455,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10465,12 +10465,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10512,24 +10512,24 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.407758</v>
+        <v>-58.481188</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.613793</v>
+        <v>-34.577198</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10541,7 +10541,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-752</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>RIVADAVIA AV. 5691</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440563</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10598,24 +10598,24 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.481188</v>
+        <v>-58.445685</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.577198</v>
+        <v>-34.622144</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10627,7 +10627,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-752</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV. 5691</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>812440563</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10684,24 +10684,24 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.445685</v>
+        <v>-58.442723</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.622144</v>
+        <v>-34.56085</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10713,7 +10713,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10770,10 +10770,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.442723</v>
+        <v>-58.481187</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.56085</v>
+        <v>-34.548301</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10799,7 +10799,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10856,24 +10856,24 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.481187</v>
+        <v>-58.414586</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.548301</v>
+        <v>-34.630095</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10942,24 +10942,24 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.414586</v>
+        <v>-58.465305</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.630095</v>
+        <v>-34.556794</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10971,22 +10971,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>CARBONARI FRANCISCO CMTE 1949</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>813046356</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11028,24 +11028,24 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.465305</v>
+        <v>-58.358919</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.556794</v>
+        <v>-34.644635</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11057,7 +11057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11067,12 +11067,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CARBONARI FRANCISCO CMTE 1949</t>
+          <t>HUMBOLDT 9</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813046356</t>
+          <t>813046372</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11095,11 +11095,7 @@
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Sin equipos</t>
@@ -11114,24 +11110,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.358919</v>
+        <v>-58.452683</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.644635</v>
+        <v>-34.598472</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11143,7 +11139,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11153,7 +11149,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HUMBOLDT 9</t>
+          <t>BURELA 1233</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11173,7 +11169,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813046372</t>
+          <t>813046378</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11181,7 +11177,11 @@
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>Sin equipos</t>
@@ -11196,10 +11196,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.452683</v>
+        <v>-58.48227</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.598472</v>
+        <v>-34.589332</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11225,7 +11225,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BURELA 1233</t>
+          <t>ALTOLAGUIRRE 1303</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813046378</t>
+          <t>813046381</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11282,10 +11282,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.48227</v>
+        <v>-58.48152</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.589332</v>
+        <v>-34.588638</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ALTOLAGUIRRE 1303</t>
+          <t>BELGRADO 3104</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>813046381</t>
+          <t>813046383</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11368,10 +11368,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.48152</v>
+        <v>-58.481007</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.588638</v>
+        <v>-34.587951</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BELGRADO 3104</t>
+          <t>MOSCU 5284</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>813046383</t>
+          <t>813046384</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11454,10 +11454,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.481007</v>
+        <v>-58.481958</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.587951</v>
+        <v>-34.587934</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MOSCU 5284</t>
+          <t>LUGONES 1736</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>813046384</t>
+          <t>813046386</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11540,14 +11540,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.481958</v>
+        <v>-58.474167</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.587934</v>
+        <v>-34.577208</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11569,7 +11569,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LUGONES 1736</t>
+          <t>ACHA, MARIANO, GRAL. 1520</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>813046386</t>
+          <t>813046388</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR  COLUMNA</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11626,10 +11626,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.474167</v>
+        <v>-58.472211</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.577208</v>
+        <v>-34.578409</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ACHA, MARIANO, GRAL. 1520</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>813046388</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>CAMBIAR  COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11712,24 +11712,24 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.472211</v>
+        <v>-58.421616</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.578409</v>
+        <v>-34.586608</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11741,7 +11741,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>ROJAS 2193</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813046393</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11798,24 +11798,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.421616</v>
+        <v>-58.454826</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.586608</v>
+        <v>-34.59885</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ROJAS 2193</t>
+          <t>BATALLA DE PARI 521</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>813046393</t>
+          <t>813046396</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11884,10 +11884,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.454826</v>
+        <v>-58.452934</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.59885</v>
+        <v>-34.599759</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11913,7 +11913,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BATALLA DE PARI 521</t>
+          <t>TRES ARROYOS 519</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>813046396</t>
+          <t>813046402</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11970,10 +11970,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.452934</v>
+        <v>-58.449879</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.599759</v>
+        <v>-34.603034</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11999,7 +11999,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TRES ARROYOS 519</t>
+          <t>SUNCHALES 514</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>813046402</t>
+          <t>813046405</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12056,10 +12056,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.449879</v>
+        <v>-58.453486</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.603034</v>
+        <v>-34.599045</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12085,7 +12085,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUNCHALES 514</t>
+          <t>SCALABRINI ORTIZ, RAUL AV. 506</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>813046405</t>
+          <t>813046410</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12142,24 +12142,24 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.453486</v>
+        <v>-58.436543</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.599045</v>
+        <v>-34.598339</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12171,7 +12171,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SCALABRINI ORTIZ, RAUL AV. 506</t>
+          <t>AGUIRRE 360</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>813046410</t>
+          <t>813046472</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12216,22 +12216,18 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.436543</v>
+        <v>-58.434568</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.598339</v>
+        <v>-34.598903</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12245,7 +12241,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12257,7 +12253,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12267,7 +12263,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AGUIRRE 360</t>
+          <t>ARAOZ 690</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12287,7 +12283,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>813046472</t>
+          <t>813046507</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12305,15 +12301,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.434568</v>
+        <v>-58.434029</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.598903</v>
+        <v>-34.597913</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARAOZ 690</t>
+          <t>CASTILLO 264</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>813046507</t>
+          <t>813046565</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12396,10 +12396,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.434029</v>
+        <v>-58.432479</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.597913</v>
+        <v>-34.59745</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CASTILLO 264</t>
+          <t>ARAOZ 878</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>813046565</t>
+          <t>813046587</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12482,10 +12482,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.432479</v>
+        <v>-58.431945</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.59745</v>
+        <v>-34.596578</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12511,17 +12511,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ARAOZ 878</t>
+          <t>LERMA 299</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12541,17 +12541,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>813046587</t>
+          <t>813046606</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12568,10 +12568,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.431945</v>
+        <v>-58.430409</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.596578</v>
+        <v>-34.595831</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12597,22 +12597,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>S00356265</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/14/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LERMA 299</t>
+          <t>RIVADAVIA MARTIN, COMODORO 2087</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12625,19 +12625,15 @@
           <t>Sin Asignar</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>813046606</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12654,24 +12650,24 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.430409</v>
+        <v>-58.465653</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.595831</v>
+        <v>-34.546494</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12683,7 +12679,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S00356265</t>
+          <t>S00387253</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12693,7 +12689,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>RIVADAVIA MARTIN, COMODORO 2087</t>
+          <t>DIAZ, CESAR, GRAL. 4881</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12736,14 +12732,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.465653</v>
+        <v>-58.49779</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.546494</v>
+        <v>-34.627626</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12753,7 +12749,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12765,7 +12761,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S00387253</t>
+          <t>S00396906</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12775,12 +12771,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 4881</t>
+          <t>MARSELLA 2546</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12818,14 +12814,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.49779</v>
+        <v>-58.477848</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.627626</v>
+        <v>-34.582559</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12835,7 +12831,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12847,7 +12843,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S00396906</t>
+          <t>S00400580</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12857,12 +12853,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MARSELLA 2546</t>
+          <t>BORDABEHERE, ENZO 2802</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12878,7 +12874,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR POSTE DE MADERA POR COLUMNA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12900,10 +12896,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.477848</v>
+        <v>-58.480405</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.582559</v>
+        <v>-34.600087</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12917,7 +12913,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12929,22 +12925,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S00400580</t>
+          <t>EXPOSITO</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4/14/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BORDABEHERE, ENZO 2802</t>
+          <t>JOSE CUBAS 2708</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12960,7 +12956,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CAMBIAR POSTE DE MADERA POR COLUMNA</t>
+          <t>Corer a línea de medianera por construcción de garage en vecino.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12970,7 +12966,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12982,10 +12978,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.480405</v>
+        <v>-58.497958</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.600087</v>
+        <v>-34.587254</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -12999,7 +12995,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13011,7 +13007,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EXPOSITO</t>
+          <t>HALVAREZ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13021,12 +13017,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>JOSE CUBAS 2708</t>
+          <t>ASUNCION 3719</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13042,7 +13038,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Corer a línea de medianera por construcción de garage en vecino.</t>
+          <t>Poste quebrado en la base. Sostenido por tendido de red telecom. Con clientes activos</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13052,7 +13048,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -13064,10 +13060,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.497958</v>
+        <v>-58.5078</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.587254</v>
+        <v>-34.598769</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13081,7 +13077,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13093,7 +13089,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HALVAREZ</t>
+          <t>MI00001</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13103,12 +13099,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ASUNCION 3719</t>
+          <t>LUGONES 2362</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13124,7 +13120,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Poste quebrado en la base. Sostenido por tendido de red telecom. Con clientes activos</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13143,17 +13139,17 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.5078</v>
+        <v>-58.479067</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.598769</v>
+        <v>-34.571679</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13163,7 +13159,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13175,7 +13171,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MI00001</t>
+          <t>GG0001</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13185,12 +13181,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LUGONES 2362</t>
+          <t>AV CABILDO 918</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13206,7 +13202,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>Cambiar columna 114 golpeada provocando dobladora a 1mts del piso.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13225,13 +13221,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.479067</v>
+        <v>-58.445962</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.571679</v>
+        <v>-34.569552</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13245,7 +13241,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13255,11 +13251,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>GG0001</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>4/20/2026</t>
@@ -13267,12 +13259,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AV CABILDO 918</t>
+          <t>AREVALO 2006</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13288,7 +13280,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Cambiar columna 114 golpeada provocando dobladora a 1mts del piso.</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13298,7 +13290,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13310,24 +13302,24 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.445962</v>
+        <v>-58.444908</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.569552</v>
+        <v>-34.607205</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13388,14 +13380,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.444908</v>
+        <v>-58.419576</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.607205</v>
+        <v>-34.621289</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13405,7 +13397,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13466,14 +13458,14 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.419576</v>
+        <v>-58.430568</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.621289</v>
+        <v>-34.599485</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13483,7 +13475,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13544,10 +13536,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.430568</v>
+        <v>-58.437499</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.599485</v>
+        <v>-34.578324</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13561,7 +13553,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13622,10 +13614,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.437499</v>
+        <v>-58.435547</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.578324</v>
+        <v>-34.576622</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13700,14 +13692,14 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.435547</v>
+        <v>-58.373629</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.576622</v>
+        <v>-34.64417</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13717,12 +13709,12 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
@@ -13735,7 +13727,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AREVALO 2006</t>
+          <t>AREVALO 2260</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13766,7 +13758,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -13778,14 +13770,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.373629</v>
+        <v>-58.444908</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.64417</v>
+        <v>-34.607205</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13795,12 +13787,12 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -13856,14 +13848,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.444908</v>
+        <v>-58.419576</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.607205</v>
+        <v>-34.621289</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13873,7 +13865,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13934,14 +13926,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.419576</v>
+        <v>-58.430568</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.621289</v>
+        <v>-34.599485</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -13951,7 +13943,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14012,10 +14004,10 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.430568</v>
+        <v>-58.437499</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.599485</v>
+        <v>-34.578324</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -14029,7 +14021,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14090,10 +14082,10 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.437499</v>
+        <v>-58.435547</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.578324</v>
+        <v>-34.576622</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -14168,14 +14160,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.435547</v>
+        <v>-58.373629</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.576622</v>
+        <v>-34.64417</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14185,12 +14177,12 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
@@ -14203,12 +14195,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AREVALO 2260</t>
+          <t>MONTES DE OCA, MANUEL AV. 1441</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14234,7 +14226,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -14246,14 +14238,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.373629</v>
+        <v>-58.444908</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.64417</v>
+        <v>-34.607205</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14263,12 +14255,12 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -14324,14 +14316,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.444908</v>
+        <v>-58.419576</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.607205</v>
+        <v>-34.621289</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14341,7 +14333,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14402,14 +14394,14 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.419576</v>
+        <v>-58.430568</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.621289</v>
+        <v>-34.599485</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14419,7 +14411,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14480,10 +14472,10 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.430568</v>
+        <v>-58.437499</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.599485</v>
+        <v>-34.578324</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -14497,7 +14489,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14558,10 +14550,10 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.437499</v>
+        <v>-58.435547</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.578324</v>
+        <v>-34.576622</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14636,14 +14628,14 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.435547</v>
+        <v>-58.373629</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.576622</v>
+        <v>-34.64417</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14653,17 +14645,21 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8879 </t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>4/20/2026</t>
@@ -14671,12 +14667,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1441</t>
+          <t>ALVAREZ THOMAS AV. 1270</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14714,36 +14710,36 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.373629</v>
+        <v>-58.459453</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.64417</v>
+        <v>-34.57843</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AL00001</t>
+          <t>GG00003</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14753,12 +14749,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1270</t>
+          <t>PEDRAZA, MANUELA 2649</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14796,14 +14792,14 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.459453</v>
+        <v>-58.468626</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.57843</v>
+        <v>-34.552938</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -14813,7 +14809,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -14825,7 +14821,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GG00003</t>
+          <t>PJ00009</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14835,12 +14831,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PEDRAZA, MANUELA 2649</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14878,24 +14874,24 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.468626</v>
+        <v>-58.431966</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.552938</v>
+        <v>-34.588553</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -14907,7 +14903,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>HT00001</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14917,12 +14913,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>CURUPAYTI 2997</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -14960,24 +14956,24 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.431966</v>
+        <v>-58.508912</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.588553</v>
+        <v>-34.580858</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -14989,22 +14985,18 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HT00001</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
+          <t>LR00001</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CURUPAYTI 2997</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15042,24 +15034,24 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.508912</v>
+        <v>-58.409695</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.580858</v>
+        <v>-34.589662</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15071,18 +15063,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LR00001</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
+          <t>PJ00040</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15103,7 +15099,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -15120,14 +15116,14 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.409695</v>
+        <v>-58.428528</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.589662</v>
+        <v>-34.589872</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15137,7 +15133,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15149,7 +15145,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15159,7 +15155,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15185,7 +15181,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -15202,10 +15198,10 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.428528</v>
+        <v>-58.413378</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.589872</v>
+        <v>-34.587254</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -15219,7 +15215,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15231,7 +15227,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15241,12 +15237,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>CULLEN 5771</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -15284,24 +15280,24 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.413378</v>
+        <v>-58.49549</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.587254</v>
+        <v>-34.577008</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15313,7 +15309,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AL00050</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15323,12 +15319,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CULLEN 5771</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15366,24 +15362,24 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.49549</v>
+        <v>-58.418851</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.577008</v>
+        <v>-34.615716</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15395,7 +15391,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15405,12 +15401,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>ARAUJO 2416</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15448,24 +15444,24 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-58.418851</v>
+        <v>-58.481107</v>
       </c>
       <c r="N178" t="n">
-        <v>-34.615716</v>
+        <v>-34.659759</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>PAV-O</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -15477,7 +15473,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AM00001</t>
+          <t>GG00035</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15487,12 +15483,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ARAUJO 2416</t>
+          <t>FIGUEROA, D. APOLINARIO, CORONEL 1793</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15508,12 +15504,12 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15530,14 +15526,14 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-58.481107</v>
+        <v>-58.461005</v>
       </c>
       <c r="N179" t="n">
-        <v>-34.659759</v>
+        <v>-34.613152</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -15547,7 +15543,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>PAV-O</t>
+          <t>NRA-J</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -15559,7 +15555,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GG00035</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15569,12 +15565,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>FIGUEROA, D. APOLINARIO, CORONEL 1793</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15590,17 +15586,17 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>APLOMAR</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -15612,24 +15608,24 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-58.461005</v>
+        <v>-58.419281</v>
       </c>
       <c r="N180" t="n">
-        <v>-34.613152</v>
+        <v>-34.62215</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>NRA-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -15641,7 +15637,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15651,12 +15647,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15682,7 +15678,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -15694,14 +15690,14 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>-58.419281</v>
+        <v>-58.41175</v>
       </c>
       <c r="N181" t="n">
-        <v>-34.62215</v>
+        <v>-34.592173</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -15711,7 +15707,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -15723,7 +15719,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LR00044</t>
+          <t>RB12120</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15733,12 +15729,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>CERRI, DANIEL, GRAL. 1214</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15776,14 +15772,14 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-58.41175</v>
+        <v>-58.366979</v>
       </c>
       <c r="N182" t="n">
-        <v>-34.592173</v>
+        <v>-34.646341</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -15793,7 +15789,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -15805,7 +15801,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RB12120</t>
+          <t>AL25250</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15815,12 +15811,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CERRI, DANIEL, GRAL. 1214</t>
+          <t>ARENAL, CONCEPCION 3526</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15846,7 +15842,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -15858,24 +15854,24 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-58.366979</v>
+        <v>-58.446573</v>
       </c>
       <c r="N183" t="n">
-        <v>-34.646341</v>
+        <v>-34.5842</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -15887,7 +15883,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AL25250</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15897,12 +15893,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3526</t>
+          <t>QUIRNO 751</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15928,7 +15924,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -15940,27 +15936,2143 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-58.446573</v>
+        <v>-58.46666</v>
       </c>
       <c r="N184" t="n">
-        <v>-34.5842</v>
+        <v>-34.640548</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>8905</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SALCEDO 3003</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-58.406395</v>
+      </c>
+      <c r="N185" t="n">
+        <v>-34.631826</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>PPT-Q</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>8906</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>VELEZ SARSFIELD AV. 139</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-58.390322</v>
+      </c>
+      <c r="N186" t="n">
+        <v>-34.635907</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>CON-K</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>8911</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BURELA 3424</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>-58.499463</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-34.568375</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>PUE-H</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AVALOS 8913</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>No clasificado, consultar con mantenimiento</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HEREDIA 1301</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-58.463223</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-34.578285</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
           <t>Colegiales</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr">
+      <c r="P189" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q184" t="inlineStr">
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>ATH-H</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>8915</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>DE LOS INCAS AV.5475</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-58.484335</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-34.588747</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>8916</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GUTENBERG 3097</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-58.499318</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-34.593795</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>PUE-Q</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>8920</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NUÑEZ 8920</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>No clasificado, consultar con mantenimiento</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DORREGO AV.2752</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-58.43266</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-34.574202</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>BLO-G</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CRAMER 4354</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-58.476561</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-34.544746</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>COG-P</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>8924</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>RIVERA PEDRO 3564</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-58.472791</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-34.563369</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>COG-I</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>8937</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ACHA, MARIANO, GRAL. 4851</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>-58.495047</v>
+      </c>
+      <c r="N196" t="n">
+        <v>-34.549483</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>COG-A</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ALSINA, ADOLFO 3293</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-58.412936</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-34.613332</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>CEN-I</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>S00419298</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AUSTRIA 2354</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-58.401523</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-34.586182</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>AGU-H</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>S00423738</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CATAMARCA 568</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-58.405541</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-34.616959</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>CEN-M</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>S00439588</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 2548</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-58.456471</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-34.564806</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>COG-F</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>8945</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>DELLEPIANE, LUIS, TTE. GRAL. 5060</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-58.474433</v>
+      </c>
+      <c r="N201" t="n">
+        <v>-34.668469</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>PAV-V</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>8953</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>TAMBORINI, JOSE PASCUAL 6010</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-58.502154</v>
+      </c>
+      <c r="N202" t="n">
+        <v>-34.57176</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>PUE-H</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>8954</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>FLORES, VENANCIO, GRAL. 4550</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>-58.490636</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-34.634459</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>DEV-M</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>LAFERRERE, GREGORIO DE 3450</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>-58.467522</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-34.642167</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>TALAVERA 5908</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="n">
+        <v>-58.499341</v>
+      </c>
+      <c r="N205" t="n">
+        <v>-34.575313</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>PUE-I</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>8969</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>BUCARELLI 1702</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="n">
+        <v>-58.482576</v>
+      </c>
+      <c r="N206" t="n">
+        <v>-34.582226</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>8973</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CARACAS 5006</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-58.497752</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-34.57947</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>PUE-I</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>8984</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>JURAMENTO 5683</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-58.488557</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-34.581502</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>PUE-C</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>8994</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>COSQUIN 296</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-58.523272</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-34.642619</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>PAV-C</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>8985</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>MAURE 4090</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-58.45208</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-34.586988</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
         <is>
           <t>ATH-L</t>
         </is>
       </c>
-      <c r="R184" t="inlineStr">
+      <c r="R210" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Sin_Asignar.xlsx
+++ b/mapa_interactivo_Sin_Asignar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R210"/>
+  <dimension ref="A1:R224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
         <v>-58.479067</v>
@@ -18073,6 +18073,1154 @@
         </is>
       </c>
       <c r="R210" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>S00299569</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>-58.425213</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-34.614924</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>ALM-D</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>S004318770</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SARMIENTO 4290</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-58.425764</v>
+      </c>
+      <c r="N212" t="n">
+        <v>-34.604359</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>ALM-L</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>S00431893</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>MUÑIZ 1151</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>-58.425442</v>
+      </c>
+      <c r="N213" t="n">
+        <v>-34.627634</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>PPT-P</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>S00434849</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-58.416028</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-34.613538</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>CEN-J</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9009 </t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SANCHEZ DE LORIA 1913</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-58.411474</v>
+      </c>
+      <c r="N215" t="n">
+        <v>-34.633143</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>PPT-Q</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9011 </t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SANCHEZ DE LORIA 1583</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-58.411926</v>
+      </c>
+      <c r="N216" t="n">
+        <v>-34.628861</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>PPT-E</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9012 </t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-58.41191</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-34.637333</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>PPT-Q</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9014 </t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>LINIERS VIRREY 896</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-58.413645</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-34.621935</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>CEN-P</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9016 </t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>HUMBERTO 1° 3368</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-58.413189</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-34.624187</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>CEN-P</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9017 </t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>MUÑIZ 1237</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-58.425206</v>
+      </c>
+      <c r="N220" t="n">
+        <v>-34.628705</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>PPT-P</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9020 </t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>TARIJA 3497</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-58.414424</v>
+      </c>
+      <c r="N221" t="n">
+        <v>-34.628778</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>PPT-E</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>S00378456</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>FRAY CAYETANO RODRIGUEZ 99</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>-58.463098</v>
+      </c>
+      <c r="N222" t="n">
+        <v>-34.627733</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>PCH-H</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>S00334047</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SAN JOSE DE CALASANZ 755</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-58.437351</v>
+      </c>
+      <c r="N223" t="n">
+        <v>-34.627956</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>PCH-C</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>S0000223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ARENALES 3660</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-58.413732</v>
+      </c>
+      <c r="N224" t="n">
+        <v>-34.585415</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>AGU-L</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>
